--- a/data/Line_Trials.xlsx
+++ b/data/Line_Trials.xlsx
@@ -1600,184 +1600,184 @@
     <xf numFmtId="0" fontId="11" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -4344,23 +4344,23 @@
       <c r="G3" s="22"/>
     </row>
     <row r="4" spans="2:36" s="1" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="G4" s="91" t="s">
+      <c r="G4" s="148" t="s">
         <v>97</v>
       </c>
-      <c r="H4" s="91"/>
-      <c r="I4" s="91"/>
-      <c r="J4" s="91"/>
-      <c r="K4" s="91"/>
-      <c r="L4" s="91"/>
+      <c r="H4" s="148"/>
+      <c r="I4" s="148"/>
+      <c r="J4" s="148"/>
+      <c r="K4" s="148"/>
+      <c r="L4" s="148"/>
       <c r="M4" s="24"/>
-      <c r="N4" s="92" t="s">
+      <c r="N4" s="117" t="s">
         <v>98</v>
       </c>
-      <c r="O4" s="93"/>
-      <c r="P4" s="93"/>
-      <c r="Q4" s="93"/>
-      <c r="R4" s="93"/>
-      <c r="S4" s="94"/>
+      <c r="O4" s="118"/>
+      <c r="P4" s="118"/>
+      <c r="Q4" s="118"/>
+      <c r="R4" s="118"/>
+      <c r="S4" s="119"/>
       <c r="T4" s="25"/>
       <c r="U4" s="2"/>
       <c r="V4" s="2"/>
@@ -4450,48 +4450,48 @@
       </c>
     </row>
     <row r="6" spans="2:36" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="95">
+      <c r="B6" s="92">
         <v>1</v>
       </c>
-      <c r="C6" s="95" t="s">
+      <c r="C6" s="92" t="s">
         <v>95</v>
       </c>
-      <c r="D6" s="96" t="s">
+      <c r="D6" s="103" t="s">
         <v>119</v>
       </c>
-      <c r="E6" s="98" t="s">
+      <c r="E6" s="138" t="s">
         <v>120</v>
       </c>
-      <c r="F6" s="100" t="s">
+      <c r="F6" s="98" t="s">
         <v>121</v>
       </c>
-      <c r="G6" s="102" t="s">
+      <c r="G6" s="115" t="s">
         <v>122</v>
       </c>
-      <c r="H6" s="103">
+      <c r="H6" s="109">
         <v>4200012365</v>
       </c>
       <c r="I6" s="38" t="s">
         <v>123</v>
       </c>
-      <c r="J6" s="103" t="s">
+      <c r="J6" s="109" t="s">
         <v>124</v>
       </c>
       <c r="K6" s="39">
         <f>2.278*(L6/(2.278*2+1.134*2))</f>
         <v>301.65807444314186</v>
       </c>
-      <c r="L6" s="110">
+      <c r="L6" s="145">
         <v>903.65</v>
       </c>
-      <c r="M6" s="111"/>
-      <c r="N6" s="95" t="s">
+      <c r="M6" s="146"/>
+      <c r="N6" s="92" t="s">
         <v>95</v>
       </c>
-      <c r="O6" s="96" t="s">
+      <c r="O6" s="103" t="s">
         <v>125</v>
       </c>
-      <c r="P6" s="103" t="s">
+      <c r="P6" s="109" t="s">
         <v>126</v>
       </c>
       <c r="Q6" s="38" t="s">
@@ -4501,53 +4501,53 @@
         <f>2.278*(S6/(2.278*2+1.134*2))</f>
         <v>282.13283704572098</v>
       </c>
-      <c r="S6" s="103">
+      <c r="S6" s="109">
         <v>845.16</v>
       </c>
       <c r="T6" s="39">
         <f>K6-R6</f>
         <v>19.525237397420881</v>
       </c>
-      <c r="U6" s="104">
+      <c r="U6" s="116">
         <f>L6-S6</f>
         <v>58.490000000000009</v>
       </c>
-      <c r="V6" s="105">
+      <c r="V6" s="136">
         <f>(U6/590)/86.6</f>
         <v>1.1447528085489493E-3</v>
       </c>
-      <c r="W6" s="106">
+      <c r="W6" s="113">
         <f>(U6/L6)*100</f>
         <v>6.4726387428761152</v>
       </c>
-      <c r="X6" s="107" t="s">
+      <c r="X6" s="106" t="s">
         <v>127</v>
       </c>
-      <c r="Y6" s="108" t="s">
+      <c r="Y6" s="137" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="7" spans="2:36" x14ac:dyDescent="0.35">
-      <c r="B7" s="95"/>
-      <c r="C7" s="95"/>
-      <c r="D7" s="97"/>
-      <c r="E7" s="99"/>
-      <c r="F7" s="101"/>
-      <c r="G7" s="102"/>
-      <c r="H7" s="103"/>
+      <c r="B7" s="92"/>
+      <c r="C7" s="92"/>
+      <c r="D7" s="104"/>
+      <c r="E7" s="140"/>
+      <c r="F7" s="99"/>
+      <c r="G7" s="115"/>
+      <c r="H7" s="109"/>
       <c r="I7" s="38" t="s">
         <v>129</v>
       </c>
-      <c r="J7" s="103"/>
+      <c r="J7" s="109"/>
       <c r="K7" s="39">
         <f>1.134*(L6/(2.278*2+1.134*2))</f>
         <v>150.16692555685816</v>
       </c>
-      <c r="L7" s="110"/>
-      <c r="M7" s="112"/>
-      <c r="N7" s="95"/>
-      <c r="O7" s="97"/>
-      <c r="P7" s="103"/>
+      <c r="L7" s="145"/>
+      <c r="M7" s="147"/>
+      <c r="N7" s="92"/>
+      <c r="O7" s="104"/>
+      <c r="P7" s="109"/>
       <c r="Q7" s="38" t="s">
         <v>129</v>
       </c>
@@ -4555,60 +4555,60 @@
         <f>1.134*(S6/(2.278*2+1.134*2))</f>
         <v>140.44716295427901</v>
       </c>
-      <c r="S7" s="103"/>
+      <c r="S7" s="109"/>
       <c r="T7" s="39">
         <f>K7-R7</f>
         <v>9.7197626025791521</v>
       </c>
-      <c r="U7" s="104"/>
-      <c r="V7" s="105"/>
-      <c r="W7" s="106"/>
-      <c r="X7" s="107"/>
-      <c r="Y7" s="108"/>
+      <c r="U7" s="116"/>
+      <c r="V7" s="136"/>
+      <c r="W7" s="113"/>
+      <c r="X7" s="106"/>
+      <c r="Y7" s="137"/>
     </row>
     <row r="8" spans="2:36" x14ac:dyDescent="0.35">
-      <c r="B8" s="95">
+      <c r="B8" s="92">
         <v>2</v>
       </c>
-      <c r="C8" s="95" t="s">
+      <c r="C8" s="92" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="96" t="s">
+      <c r="D8" s="103" t="s">
         <v>119</v>
       </c>
-      <c r="E8" s="109" t="s">
+      <c r="E8" s="114" t="s">
         <v>130</v>
       </c>
-      <c r="F8" s="100" t="s">
+      <c r="F8" s="98" t="s">
         <v>121</v>
       </c>
-      <c r="G8" s="102" t="s">
+      <c r="G8" s="115" t="s">
         <v>58</v>
       </c>
-      <c r="H8" s="103">
+      <c r="H8" s="109">
         <v>6000004204</v>
       </c>
       <c r="I8" s="38" t="s">
         <v>123</v>
       </c>
-      <c r="J8" s="103" t="s">
+      <c r="J8" s="109" t="s">
         <v>131</v>
       </c>
       <c r="K8" s="39">
         <f>2.278*(L8/(2.278*2+1.134*2))</f>
         <v>2.8374853458382181</v>
       </c>
-      <c r="L8" s="110">
+      <c r="L8" s="145">
         <v>8.5</v>
       </c>
-      <c r="M8" s="111"/>
-      <c r="N8" s="95" t="s">
+      <c r="M8" s="146"/>
+      <c r="N8" s="92" t="s">
         <v>13</v>
       </c>
-      <c r="O8" s="103" t="s">
+      <c r="O8" s="109" t="s">
         <v>130</v>
       </c>
-      <c r="P8" s="96" t="s">
+      <c r="P8" s="103" t="s">
         <v>93</v>
       </c>
       <c r="Q8" s="38" t="s">
@@ -4618,53 +4618,53 @@
         <f>2.278*(S8/(2.278*2+1.134*2))</f>
         <v>2.7173094958968349</v>
       </c>
-      <c r="S8" s="96">
+      <c r="S8" s="103">
         <v>8.14</v>
       </c>
       <c r="T8" s="39">
         <f>K8-R8</f>
         <v>0.12017584994138319</v>
       </c>
-      <c r="U8" s="104">
+      <c r="U8" s="116">
         <f>T8+T9</f>
         <v>0.17999999999999972</v>
       </c>
-      <c r="V8" s="105">
+      <c r="V8" s="136">
         <f>(U8/590)</f>
         <v>3.0508474576271136E-4</v>
       </c>
-      <c r="W8" s="106">
+      <c r="W8" s="113">
         <f>(U8/L8)*100</f>
         <v>2.1176470588235263</v>
       </c>
-      <c r="X8" s="107" t="s">
+      <c r="X8" s="106" t="s">
         <v>132</v>
       </c>
-      <c r="Y8" s="108" t="s">
+      <c r="Y8" s="137" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="9" spans="2:36" x14ac:dyDescent="0.35">
-      <c r="B9" s="95"/>
-      <c r="C9" s="95"/>
-      <c r="D9" s="97"/>
-      <c r="E9" s="109"/>
-      <c r="F9" s="101"/>
-      <c r="G9" s="102"/>
-      <c r="H9" s="103"/>
+      <c r="B9" s="92"/>
+      <c r="C9" s="92"/>
+      <c r="D9" s="104"/>
+      <c r="E9" s="114"/>
+      <c r="F9" s="99"/>
+      <c r="G9" s="115"/>
+      <c r="H9" s="109"/>
       <c r="I9" s="38" t="s">
         <v>129</v>
       </c>
-      <c r="J9" s="103"/>
+      <c r="J9" s="109"/>
       <c r="K9" s="46">
         <f>1.134*(L8/(2.278*2+1.134*2))</f>
         <v>1.4125146541617817</v>
       </c>
-      <c r="L9" s="110"/>
-      <c r="M9" s="112"/>
-      <c r="N9" s="95"/>
-      <c r="O9" s="103"/>
-      <c r="P9" s="97"/>
+      <c r="L9" s="145"/>
+      <c r="M9" s="147"/>
+      <c r="N9" s="92"/>
+      <c r="O9" s="109"/>
+      <c r="P9" s="104"/>
       <c r="Q9" s="38" t="s">
         <v>129</v>
       </c>
@@ -4672,16 +4672,16 @@
         <f>1.134*(S8/(2.278*2+1.134*2))</f>
         <v>1.3526905041031652</v>
       </c>
-      <c r="S9" s="97"/>
+      <c r="S9" s="104"/>
       <c r="T9" s="39">
         <f>K9-R9</f>
         <v>5.9824150058616521E-2</v>
       </c>
-      <c r="U9" s="104"/>
-      <c r="V9" s="105"/>
-      <c r="W9" s="106"/>
-      <c r="X9" s="107"/>
-      <c r="Y9" s="108"/>
+      <c r="U9" s="116"/>
+      <c r="V9" s="136"/>
+      <c r="W9" s="113"/>
+      <c r="X9" s="106"/>
+      <c r="Y9" s="137"/>
     </row>
     <row r="10" spans="2:36" x14ac:dyDescent="0.35">
       <c r="B10" s="3">
@@ -4746,7 +4746,7 @@
         <f>L10-S10</f>
         <v>-2.2099999999999795</v>
       </c>
-      <c r="V10" s="105">
+      <c r="V10" s="136">
         <f>(U10/590)</f>
         <v>-3.7457627118643723E-3</v>
       </c>
@@ -4783,53 +4783,53 @@
       </c>
       <c r="T11" s="50"/>
       <c r="U11" s="18"/>
-      <c r="V11" s="105"/>
+      <c r="V11" s="136"/>
       <c r="W11" s="55"/>
     </row>
     <row r="12" spans="2:36" x14ac:dyDescent="0.35">
-      <c r="B12" s="95">
+      <c r="B12" s="92">
         <v>4</v>
       </c>
-      <c r="C12" s="95" t="s">
+      <c r="C12" s="92" t="s">
         <v>13</v>
       </c>
-      <c r="D12" s="96" t="s">
+      <c r="D12" s="103" t="s">
         <v>142</v>
       </c>
-      <c r="E12" s="100" t="s">
+      <c r="E12" s="98" t="s">
         <v>130</v>
       </c>
-      <c r="F12" s="100" t="s">
+      <c r="F12" s="98" t="s">
         <v>143</v>
       </c>
-      <c r="G12" s="100" t="s">
+      <c r="G12" s="98" t="s">
         <v>144</v>
       </c>
-      <c r="H12" s="100">
+      <c r="H12" s="98">
         <v>6000004401</v>
       </c>
       <c r="I12" s="38" t="s">
         <v>145</v>
       </c>
-      <c r="J12" s="103" t="s">
+      <c r="J12" s="109" t="s">
         <v>146</v>
       </c>
       <c r="K12" s="56">
         <f>0.9*86.14</f>
         <v>77.525999999999996</v>
       </c>
-      <c r="L12" s="113">
+      <c r="L12" s="100">
         <f>K12+K13</f>
         <v>142.9924</v>
       </c>
-      <c r="M12" s="115"/>
-      <c r="N12" s="95" t="s">
+      <c r="M12" s="111"/>
+      <c r="N12" s="92" t="s">
         <v>95</v>
       </c>
-      <c r="O12" s="95" t="s">
+      <c r="O12" s="92" t="s">
         <v>135</v>
       </c>
-      <c r="P12" s="96" t="s">
+      <c r="P12" s="103" t="s">
         <v>147</v>
       </c>
       <c r="Q12" s="3" t="s">
@@ -4838,7 +4838,7 @@
       <c r="R12" s="38">
         <v>86</v>
       </c>
-      <c r="S12" s="96">
+      <c r="S12" s="103">
         <f>R12+R13</f>
         <v>165</v>
       </c>
@@ -4846,105 +4846,105 @@
         <f>K12-R12</f>
         <v>-8.4740000000000038</v>
       </c>
-      <c r="U12" s="106">
+      <c r="U12" s="113">
         <f>L12-S12</f>
         <v>-22.007599999999996</v>
       </c>
-      <c r="V12" s="117">
+      <c r="V12" s="95">
         <f>U12/590</f>
         <v>-3.7301016949152534E-2</v>
       </c>
-      <c r="W12" s="106">
+      <c r="W12" s="113">
         <f>(U12/L12)*100</f>
         <v>-15.390748039755955</v>
       </c>
-      <c r="X12" s="95" t="s">
+      <c r="X12" s="92" t="s">
         <v>149</v>
       </c>
-      <c r="Y12" s="108" t="s">
+      <c r="Y12" s="137" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="13" spans="2:36" x14ac:dyDescent="0.35">
-      <c r="B13" s="95"/>
-      <c r="C13" s="95"/>
-      <c r="D13" s="97"/>
-      <c r="E13" s="101"/>
-      <c r="F13" s="101"/>
-      <c r="G13" s="101"/>
-      <c r="H13" s="101"/>
+      <c r="B13" s="92"/>
+      <c r="C13" s="92"/>
+      <c r="D13" s="104"/>
+      <c r="E13" s="99"/>
+      <c r="F13" s="99"/>
+      <c r="G13" s="99"/>
+      <c r="H13" s="99"/>
       <c r="I13" s="38" t="s">
         <v>150</v>
       </c>
-      <c r="J13" s="103"/>
+      <c r="J13" s="109"/>
       <c r="K13" s="56">
         <f>0.76*86.14</f>
         <v>65.466400000000007</v>
       </c>
-      <c r="L13" s="114"/>
-      <c r="M13" s="116"/>
-      <c r="N13" s="95"/>
-      <c r="O13" s="95"/>
-      <c r="P13" s="97"/>
+      <c r="L13" s="101"/>
+      <c r="M13" s="112"/>
+      <c r="N13" s="92"/>
+      <c r="O13" s="92"/>
+      <c r="P13" s="104"/>
       <c r="Q13" s="49" t="s">
         <v>151</v>
       </c>
       <c r="R13" s="38">
         <v>79</v>
       </c>
-      <c r="S13" s="97"/>
+      <c r="S13" s="104"/>
       <c r="T13" s="39">
         <f t="shared" ref="T13:T18" si="0">K13-R13</f>
         <v>-13.533599999999993</v>
       </c>
-      <c r="U13" s="106"/>
-      <c r="V13" s="118"/>
-      <c r="W13" s="106"/>
-      <c r="X13" s="95"/>
-      <c r="Y13" s="108"/>
+      <c r="U13" s="113"/>
+      <c r="V13" s="96"/>
+      <c r="W13" s="113"/>
+      <c r="X13" s="92"/>
+      <c r="Y13" s="137"/>
     </row>
     <row r="14" spans="2:36" x14ac:dyDescent="0.35">
-      <c r="B14" s="95">
+      <c r="B14" s="92">
         <v>5</v>
       </c>
-      <c r="C14" s="95" t="s">
+      <c r="C14" s="92" t="s">
         <v>25</v>
       </c>
-      <c r="D14" s="96" t="s">
+      <c r="D14" s="103" t="s">
         <v>142</v>
       </c>
-      <c r="E14" s="109" t="s">
+      <c r="E14" s="114" t="s">
         <v>130</v>
       </c>
-      <c r="F14" s="100" t="s">
+      <c r="F14" s="98" t="s">
         <v>143</v>
       </c>
-      <c r="G14" s="102" t="s">
+      <c r="G14" s="115" t="s">
         <v>152</v>
       </c>
-      <c r="H14" s="95">
+      <c r="H14" s="92">
         <v>6000004174</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="J14" s="103" t="s">
+      <c r="J14" s="109" t="s">
         <v>124</v>
       </c>
       <c r="K14" s="56">
         <v>207.5</v>
       </c>
-      <c r="L14" s="125">
+      <c r="L14" s="110">
         <v>382.5</v>
       </c>
-      <c r="M14" s="115"/>
-      <c r="N14" s="95" t="s">
+      <c r="M14" s="111"/>
+      <c r="N14" s="92" t="s">
         <v>25</v>
       </c>
-      <c r="O14" s="95" t="s">
+      <c r="O14" s="92" t="s">
         <v>130</v>
       </c>
-      <c r="P14" s="96" t="s">
+      <c r="P14" s="103" t="s">
         <v>154</v>
       </c>
       <c r="Q14" s="3" t="s">
@@ -4953,112 +4953,112 @@
       <c r="R14" s="38">
         <v>200</v>
       </c>
-      <c r="S14" s="96">
+      <c r="S14" s="103">
         <v>370</v>
       </c>
       <c r="T14" s="38">
         <f t="shared" si="0"/>
         <v>7.5</v>
       </c>
-      <c r="U14" s="104">
+      <c r="U14" s="116">
         <f>L14-S14</f>
         <v>12.5</v>
       </c>
-      <c r="V14" s="117">
+      <c r="V14" s="95">
         <f>U14/590</f>
         <v>2.1186440677966101E-2</v>
       </c>
-      <c r="W14" s="106">
+      <c r="W14" s="113">
         <f>(U14/L14)*100</f>
         <v>3.2679738562091507</v>
       </c>
-      <c r="X14" s="95" t="s">
+      <c r="X14" s="92" t="s">
         <v>155</v>
       </c>
-      <c r="Y14" s="108" t="s">
+      <c r="Y14" s="137" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="15" spans="2:36" x14ac:dyDescent="0.35">
-      <c r="B15" s="95"/>
-      <c r="C15" s="95"/>
-      <c r="D15" s="97"/>
-      <c r="E15" s="109"/>
-      <c r="F15" s="101"/>
-      <c r="G15" s="102"/>
-      <c r="H15" s="95"/>
+      <c r="B15" s="92"/>
+      <c r="C15" s="92"/>
+      <c r="D15" s="104"/>
+      <c r="E15" s="114"/>
+      <c r="F15" s="99"/>
+      <c r="G15" s="115"/>
+      <c r="H15" s="92"/>
       <c r="I15" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="J15" s="103"/>
+      <c r="J15" s="109"/>
       <c r="K15" s="56">
         <v>175</v>
       </c>
-      <c r="L15" s="125"/>
-      <c r="M15" s="116"/>
-      <c r="N15" s="95"/>
-      <c r="O15" s="95"/>
-      <c r="P15" s="97"/>
+      <c r="L15" s="110"/>
+      <c r="M15" s="112"/>
+      <c r="N15" s="92"/>
+      <c r="O15" s="92"/>
+      <c r="P15" s="104"/>
       <c r="Q15" s="49" t="s">
         <v>151</v>
       </c>
       <c r="R15" s="38">
         <v>170</v>
       </c>
-      <c r="S15" s="97"/>
+      <c r="S15" s="104"/>
       <c r="T15" s="38">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="U15" s="104"/>
-      <c r="V15" s="118"/>
-      <c r="W15" s="106"/>
-      <c r="X15" s="95"/>
-      <c r="Y15" s="108"/>
+      <c r="U15" s="116"/>
+      <c r="V15" s="96"/>
+      <c r="W15" s="113"/>
+      <c r="X15" s="92"/>
+      <c r="Y15" s="137"/>
     </row>
     <row r="16" spans="2:36" x14ac:dyDescent="0.35">
-      <c r="B16" s="100">
+      <c r="B16" s="98">
         <v>6</v>
       </c>
-      <c r="C16" s="100" t="s">
+      <c r="C16" s="98" t="s">
         <v>95</v>
       </c>
       <c r="D16" s="38" t="s">
         <v>70</v>
       </c>
-      <c r="E16" s="98" t="s">
+      <c r="E16" s="138" t="s">
         <v>135</v>
       </c>
-      <c r="F16" s="100" t="s">
+      <c r="F16" s="98" t="s">
         <v>157</v>
       </c>
-      <c r="G16" s="121" t="s">
+      <c r="G16" s="141" t="s">
         <v>158</v>
       </c>
-      <c r="H16" s="100">
+      <c r="H16" s="98">
         <v>4200012518</v>
       </c>
       <c r="I16" s="38" t="s">
         <v>70</v>
       </c>
-      <c r="J16" s="100" t="s">
+      <c r="J16" s="98" t="s">
         <v>124</v>
       </c>
       <c r="K16" s="56">
         <v>129.63</v>
       </c>
-      <c r="L16" s="115">
+      <c r="L16" s="111">
         <f>K16+K17+K18</f>
         <v>590.73</v>
       </c>
-      <c r="M16" s="115"/>
-      <c r="N16" s="100" t="s">
+      <c r="M16" s="111"/>
+      <c r="N16" s="98" t="s">
         <v>95</v>
       </c>
-      <c r="O16" s="100" t="s">
+      <c r="O16" s="98" t="s">
         <v>135</v>
       </c>
-      <c r="P16" s="103" t="s">
+      <c r="P16" s="109" t="s">
         <v>159</v>
       </c>
       <c r="Q16" s="38" t="s">
@@ -5067,7 +5067,7 @@
       <c r="R16" s="38">
         <v>129</v>
       </c>
-      <c r="S16" s="96">
+      <c r="S16" s="103">
         <f>R16+R17+R18</f>
         <v>585</v>
       </c>
@@ -5075,22 +5075,22 @@
         <f t="shared" si="0"/>
         <v>0.62999999999999545</v>
       </c>
-      <c r="U16" s="128">
+      <c r="U16" s="127">
         <f>L16-S16</f>
         <v>5.7300000000000182</v>
       </c>
-      <c r="V16" s="117">
+      <c r="V16" s="95">
         <f>U16/590</f>
         <v>9.7118644067796921E-3</v>
       </c>
-      <c r="W16" s="132">
+      <c r="W16" s="93">
         <f>(U16/L16)*100</f>
         <v>0.96998628815195065</v>
       </c>
-      <c r="X16" s="113" t="s">
+      <c r="X16" s="100" t="s">
         <v>160</v>
       </c>
-      <c r="Y16" s="108" t="s">
+      <c r="Y16" s="137" t="s">
         <v>161</v>
       </c>
       <c r="AG16" s="58" t="s">
@@ -5107,43 +5107,43 @@
       </c>
     </row>
     <row r="17" spans="2:36" x14ac:dyDescent="0.35">
-      <c r="B17" s="119"/>
-      <c r="C17" s="119"/>
+      <c r="B17" s="121"/>
+      <c r="C17" s="121"/>
       <c r="D17" s="38" t="s">
         <v>162</v>
       </c>
-      <c r="E17" s="120"/>
-      <c r="F17" s="119"/>
-      <c r="G17" s="122"/>
-      <c r="H17" s="119"/>
+      <c r="E17" s="139"/>
+      <c r="F17" s="121"/>
+      <c r="G17" s="142"/>
+      <c r="H17" s="121"/>
       <c r="I17" s="38" t="s">
         <v>162</v>
       </c>
-      <c r="J17" s="119"/>
+      <c r="J17" s="121"/>
       <c r="K17" s="46">
         <v>230.55</v>
       </c>
-      <c r="L17" s="124"/>
-      <c r="M17" s="124"/>
-      <c r="N17" s="119"/>
-      <c r="O17" s="119"/>
-      <c r="P17" s="103"/>
+      <c r="L17" s="144"/>
+      <c r="M17" s="144"/>
+      <c r="N17" s="121"/>
+      <c r="O17" s="121"/>
+      <c r="P17" s="109"/>
       <c r="Q17" s="38" t="s">
         <v>162</v>
       </c>
       <c r="R17" s="38">
         <v>228</v>
       </c>
-      <c r="S17" s="127"/>
+      <c r="S17" s="126"/>
       <c r="T17" s="38">
         <f t="shared" si="0"/>
         <v>2.5500000000000114</v>
       </c>
-      <c r="U17" s="129"/>
-      <c r="V17" s="131"/>
-      <c r="W17" s="133"/>
-      <c r="X17" s="126"/>
-      <c r="Y17" s="108"/>
+      <c r="U17" s="128"/>
+      <c r="V17" s="135"/>
+      <c r="W17" s="120"/>
+      <c r="X17" s="125"/>
+      <c r="Y17" s="137"/>
       <c r="AG17" s="58" t="s">
         <v>163</v>
       </c>
@@ -5159,43 +5159,43 @@
       </c>
     </row>
     <row r="18" spans="2:36" x14ac:dyDescent="0.35">
-      <c r="B18" s="101"/>
-      <c r="C18" s="101"/>
+      <c r="B18" s="99"/>
+      <c r="C18" s="99"/>
       <c r="D18" s="38" t="s">
         <v>164</v>
       </c>
-      <c r="E18" s="99"/>
-      <c r="F18" s="101"/>
-      <c r="G18" s="123"/>
-      <c r="H18" s="101"/>
+      <c r="E18" s="140"/>
+      <c r="F18" s="99"/>
+      <c r="G18" s="143"/>
+      <c r="H18" s="99"/>
       <c r="I18" s="38" t="s">
         <v>164</v>
       </c>
-      <c r="J18" s="101"/>
+      <c r="J18" s="99"/>
       <c r="K18" s="46">
         <v>230.55</v>
       </c>
-      <c r="L18" s="116"/>
-      <c r="M18" s="116"/>
-      <c r="N18" s="101"/>
-      <c r="O18" s="101"/>
-      <c r="P18" s="103"/>
+      <c r="L18" s="112"/>
+      <c r="M18" s="112"/>
+      <c r="N18" s="99"/>
+      <c r="O18" s="99"/>
+      <c r="P18" s="109"/>
       <c r="Q18" s="38" t="s">
         <v>164</v>
       </c>
       <c r="R18" s="38">
         <v>228</v>
       </c>
-      <c r="S18" s="97"/>
+      <c r="S18" s="104"/>
       <c r="T18" s="38">
         <f t="shared" si="0"/>
         <v>2.5500000000000114</v>
       </c>
-      <c r="U18" s="130"/>
-      <c r="V18" s="118"/>
-      <c r="W18" s="134"/>
-      <c r="X18" s="114"/>
-      <c r="Y18" s="108"/>
+      <c r="U18" s="94"/>
+      <c r="V18" s="96"/>
+      <c r="W18" s="97"/>
+      <c r="X18" s="101"/>
+      <c r="Y18" s="137"/>
       <c r="AG18" s="58" t="s">
         <v>142</v>
       </c>
@@ -5211,48 +5211,48 @@
       </c>
     </row>
     <row r="19" spans="2:36" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="100">
+      <c r="B19" s="98">
         <v>7</v>
       </c>
-      <c r="C19" s="100" t="s">
+      <c r="C19" s="98" t="s">
         <v>25</v>
       </c>
-      <c r="D19" s="96" t="s">
+      <c r="D19" s="103" t="s">
         <v>46</v>
       </c>
-      <c r="E19" s="96" t="s">
+      <c r="E19" s="103" t="s">
         <v>130</v>
       </c>
-      <c r="F19" s="100" t="s">
+      <c r="F19" s="98" t="s">
         <v>157</v>
       </c>
-      <c r="G19" s="96" t="s">
+      <c r="G19" s="103" t="s">
         <v>165</v>
       </c>
-      <c r="H19" s="100">
+      <c r="H19" s="98">
         <v>6000004468</v>
       </c>
       <c r="I19" s="38" t="s">
         <v>166</v>
       </c>
-      <c r="J19" s="113" t="s">
+      <c r="J19" s="100" t="s">
         <v>131</v>
       </c>
       <c r="K19" s="49">
         <v>13.58</v>
       </c>
-      <c r="L19" s="100">
+      <c r="L19" s="98">
         <f>K19+K20+K21</f>
         <v>38.540000000000006</v>
       </c>
-      <c r="M19" s="100"/>
-      <c r="N19" s="113" t="s">
+      <c r="M19" s="98"/>
+      <c r="N19" s="100" t="s">
         <v>167</v>
       </c>
-      <c r="O19" s="100" t="s">
+      <c r="O19" s="98" t="s">
         <v>130</v>
       </c>
-      <c r="P19" s="96" t="s">
+      <c r="P19" s="103" t="s">
         <v>168</v>
       </c>
       <c r="Q19" s="38" t="s">
@@ -5261,7 +5261,7 @@
       <c r="R19" s="38">
         <v>13.8</v>
       </c>
-      <c r="S19" s="96">
+      <c r="S19" s="103">
         <f>R19+R20+R21</f>
         <v>40</v>
       </c>
@@ -5269,22 +5269,22 @@
         <f>K19-R19</f>
         <v>-0.22000000000000064</v>
       </c>
-      <c r="U19" s="128">
+      <c r="U19" s="127">
         <f>L19-S19</f>
         <v>-1.4599999999999937</v>
       </c>
-      <c r="V19" s="117">
+      <c r="V19" s="95">
         <f>U19/590</f>
         <v>-2.4745762711864301E-3</v>
       </c>
-      <c r="W19" s="132">
+      <c r="W19" s="93">
         <f>(U19/L19)*100</f>
         <v>-3.7882719252724275</v>
       </c>
-      <c r="X19" s="100" t="s">
+      <c r="X19" s="98" t="s">
         <v>132</v>
       </c>
-      <c r="Y19" s="135"/>
+      <c r="Y19" s="122"/>
       <c r="AG19" s="58" t="s">
         <v>169</v>
       </c>
@@ -5298,41 +5298,41 @@
       </c>
     </row>
     <row r="20" spans="2:36" x14ac:dyDescent="0.35">
-      <c r="B20" s="119"/>
-      <c r="C20" s="119"/>
-      <c r="D20" s="127"/>
-      <c r="E20" s="127"/>
-      <c r="F20" s="119"/>
-      <c r="G20" s="127"/>
-      <c r="H20" s="119"/>
+      <c r="B20" s="121"/>
+      <c r="C20" s="121"/>
+      <c r="D20" s="126"/>
+      <c r="E20" s="126"/>
+      <c r="F20" s="121"/>
+      <c r="G20" s="126"/>
+      <c r="H20" s="121"/>
       <c r="I20" s="38" t="s">
         <v>170</v>
       </c>
-      <c r="J20" s="126"/>
+      <c r="J20" s="125"/>
       <c r="K20" s="49">
         <v>12.48</v>
       </c>
-      <c r="L20" s="119"/>
-      <c r="M20" s="101"/>
-      <c r="N20" s="126"/>
-      <c r="O20" s="119"/>
-      <c r="P20" s="127"/>
+      <c r="L20" s="121"/>
+      <c r="M20" s="99"/>
+      <c r="N20" s="125"/>
+      <c r="O20" s="121"/>
+      <c r="P20" s="126"/>
       <c r="Q20" s="38" t="s">
         <v>170</v>
       </c>
       <c r="R20" s="49">
         <v>13.1</v>
       </c>
-      <c r="S20" s="127"/>
+      <c r="S20" s="126"/>
       <c r="T20" s="38">
         <f t="shared" ref="T20:T42" si="2">K20-R20</f>
         <v>-0.61999999999999922</v>
       </c>
-      <c r="U20" s="129"/>
-      <c r="V20" s="131"/>
-      <c r="W20" s="133"/>
-      <c r="X20" s="119"/>
-      <c r="Y20" s="136"/>
+      <c r="U20" s="128"/>
+      <c r="V20" s="135"/>
+      <c r="W20" s="120"/>
+      <c r="X20" s="121"/>
+      <c r="Y20" s="123"/>
       <c r="AG20" s="58" t="s">
         <v>171</v>
       </c>
@@ -5346,41 +5346,41 @@
       </c>
     </row>
     <row r="21" spans="2:36" x14ac:dyDescent="0.35">
-      <c r="B21" s="101"/>
-      <c r="C21" s="101"/>
-      <c r="D21" s="97"/>
-      <c r="E21" s="97"/>
-      <c r="F21" s="101"/>
-      <c r="G21" s="97"/>
-      <c r="H21" s="101"/>
+      <c r="B21" s="99"/>
+      <c r="C21" s="99"/>
+      <c r="D21" s="104"/>
+      <c r="E21" s="104"/>
+      <c r="F21" s="99"/>
+      <c r="G21" s="104"/>
+      <c r="H21" s="99"/>
       <c r="I21" s="38" t="s">
         <v>172</v>
       </c>
-      <c r="J21" s="114"/>
+      <c r="J21" s="101"/>
       <c r="K21" s="49">
         <v>12.48</v>
       </c>
-      <c r="L21" s="101"/>
+      <c r="L21" s="99"/>
       <c r="M21" s="43"/>
-      <c r="N21" s="114"/>
-      <c r="O21" s="101"/>
-      <c r="P21" s="97"/>
+      <c r="N21" s="101"/>
+      <c r="O21" s="99"/>
+      <c r="P21" s="104"/>
       <c r="Q21" s="38" t="s">
         <v>172</v>
       </c>
       <c r="R21" s="49">
         <v>13.1</v>
       </c>
-      <c r="S21" s="97"/>
+      <c r="S21" s="104"/>
       <c r="T21" s="38">
         <f>K21-R21</f>
         <v>-0.61999999999999922</v>
       </c>
-      <c r="U21" s="130"/>
-      <c r="V21" s="118"/>
-      <c r="W21" s="134"/>
-      <c r="X21" s="101"/>
-      <c r="Y21" s="137"/>
+      <c r="U21" s="94"/>
+      <c r="V21" s="96"/>
+      <c r="W21" s="97"/>
+      <c r="X21" s="99"/>
+      <c r="Y21" s="124"/>
       <c r="AG21" s="58" t="s">
         <v>32</v>
       </c>
@@ -5394,48 +5394,48 @@
       </c>
     </row>
     <row r="22" spans="2:36" x14ac:dyDescent="0.35">
-      <c r="B22" s="100">
+      <c r="B22" s="98">
         <v>8</v>
       </c>
-      <c r="C22" s="100" t="s">
+      <c r="C22" s="98" t="s">
         <v>25</v>
       </c>
-      <c r="D22" s="100" t="s">
+      <c r="D22" s="98" t="s">
         <v>173</v>
       </c>
-      <c r="E22" s="100" t="s">
+      <c r="E22" s="98" t="s">
         <v>130</v>
       </c>
-      <c r="F22" s="100" t="s">
+      <c r="F22" s="98" t="s">
         <v>157</v>
       </c>
-      <c r="G22" s="113" t="s">
+      <c r="G22" s="100" t="s">
         <v>174</v>
       </c>
-      <c r="H22" s="100">
+      <c r="H22" s="98">
         <v>6000004458</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="J22" s="113" t="s">
+      <c r="J22" s="100" t="s">
         <v>131</v>
       </c>
       <c r="K22" s="60">
         <v>1.22</v>
       </c>
-      <c r="L22" s="113">
+      <c r="L22" s="100">
         <f>K22+K23+K24</f>
         <v>5.96</v>
       </c>
       <c r="M22" s="61"/>
-      <c r="N22" s="113" t="s">
+      <c r="N22" s="100" t="s">
         <v>25</v>
       </c>
-      <c r="O22" s="113" t="s">
+      <c r="O22" s="100" t="s">
         <v>130</v>
       </c>
-      <c r="P22" s="96" t="s">
+      <c r="P22" s="103" t="s">
         <v>176</v>
       </c>
       <c r="Q22" s="38" t="s">
@@ -5444,7 +5444,7 @@
       <c r="R22" s="3">
         <v>1.28</v>
       </c>
-      <c r="S22" s="95">
+      <c r="S22" s="92">
         <f>R22+R23+R24</f>
         <v>6.04</v>
       </c>
@@ -5452,22 +5452,22 @@
         <f t="shared" si="2"/>
         <v>-6.0000000000000053E-2</v>
       </c>
-      <c r="U22" s="104">
+      <c r="U22" s="116">
         <f>L22-S22</f>
         <v>-8.0000000000000071E-2</v>
       </c>
-      <c r="V22" s="105">
+      <c r="V22" s="136">
         <f>U22/590</f>
         <v>-1.3559322033898318E-4</v>
       </c>
-      <c r="W22" s="132">
+      <c r="W22" s="93">
         <f>(U22/L22)*100</f>
         <v>-1.342281879194632</v>
       </c>
-      <c r="X22" s="100" t="s">
+      <c r="X22" s="98" t="s">
         <v>132</v>
       </c>
-      <c r="Y22" s="135"/>
+      <c r="Y22" s="122"/>
       <c r="AG22" s="23" t="s">
         <v>70</v>
       </c>
@@ -5481,126 +5481,126 @@
       </c>
     </row>
     <row r="23" spans="2:36" x14ac:dyDescent="0.35">
-      <c r="B23" s="119"/>
-      <c r="C23" s="119"/>
-      <c r="D23" s="119"/>
-      <c r="E23" s="119"/>
-      <c r="F23" s="119"/>
-      <c r="G23" s="126"/>
-      <c r="H23" s="119"/>
+      <c r="B23" s="121"/>
+      <c r="C23" s="121"/>
+      <c r="D23" s="121"/>
+      <c r="E23" s="121"/>
+      <c r="F23" s="121"/>
+      <c r="G23" s="125"/>
+      <c r="H23" s="121"/>
       <c r="I23" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="J23" s="126"/>
+      <c r="J23" s="125"/>
       <c r="K23" s="60">
         <v>2.37</v>
       </c>
-      <c r="L23" s="126"/>
+      <c r="L23" s="125"/>
       <c r="M23" s="61"/>
-      <c r="N23" s="126"/>
-      <c r="O23" s="126"/>
-      <c r="P23" s="127"/>
+      <c r="N23" s="125"/>
+      <c r="O23" s="125"/>
+      <c r="P23" s="126"/>
       <c r="Q23" s="38" t="s">
         <v>162</v>
       </c>
       <c r="R23" s="3">
         <v>2.38</v>
       </c>
-      <c r="S23" s="95"/>
+      <c r="S23" s="92"/>
       <c r="T23" s="49">
         <f t="shared" si="2"/>
         <v>-9.9999999999997868E-3</v>
       </c>
-      <c r="U23" s="104"/>
-      <c r="V23" s="105"/>
-      <c r="W23" s="133"/>
-      <c r="X23" s="119"/>
-      <c r="Y23" s="136"/>
+      <c r="U23" s="116"/>
+      <c r="V23" s="136"/>
+      <c r="W23" s="120"/>
+      <c r="X23" s="121"/>
+      <c r="Y23" s="123"/>
       <c r="AJ23" s="10">
         <v>3800000</v>
       </c>
     </row>
     <row r="24" spans="2:36" x14ac:dyDescent="0.35">
-      <c r="B24" s="101"/>
-      <c r="C24" s="101"/>
-      <c r="D24" s="101"/>
-      <c r="E24" s="101"/>
-      <c r="F24" s="101"/>
-      <c r="G24" s="114"/>
-      <c r="H24" s="101"/>
+      <c r="B24" s="99"/>
+      <c r="C24" s="99"/>
+      <c r="D24" s="99"/>
+      <c r="E24" s="99"/>
+      <c r="F24" s="99"/>
+      <c r="G24" s="101"/>
+      <c r="H24" s="99"/>
       <c r="I24" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="J24" s="114"/>
+      <c r="J24" s="101"/>
       <c r="K24" s="60">
         <v>2.37</v>
       </c>
-      <c r="L24" s="114"/>
+      <c r="L24" s="101"/>
       <c r="M24" s="61"/>
-      <c r="N24" s="114"/>
-      <c r="O24" s="114"/>
-      <c r="P24" s="127"/>
+      <c r="N24" s="101"/>
+      <c r="O24" s="101"/>
+      <c r="P24" s="126"/>
       <c r="Q24" s="37" t="s">
         <v>164</v>
       </c>
       <c r="R24" s="3">
         <v>2.38</v>
       </c>
-      <c r="S24" s="95"/>
+      <c r="S24" s="92"/>
       <c r="T24" s="49">
         <f t="shared" si="2"/>
         <v>-9.9999999999997868E-3</v>
       </c>
-      <c r="U24" s="104"/>
-      <c r="V24" s="105"/>
-      <c r="W24" s="134"/>
-      <c r="X24" s="101"/>
-      <c r="Y24" s="137"/>
+      <c r="U24" s="116"/>
+      <c r="V24" s="136"/>
+      <c r="W24" s="97"/>
+      <c r="X24" s="99"/>
+      <c r="Y24" s="124"/>
     </row>
     <row r="25" spans="2:36" x14ac:dyDescent="0.35">
-      <c r="B25" s="100">
+      <c r="B25" s="98">
         <v>9</v>
       </c>
-      <c r="C25" s="100" t="s">
+      <c r="C25" s="98" t="s">
         <v>13</v>
       </c>
-      <c r="D25" s="96" t="s">
+      <c r="D25" s="103" t="s">
         <v>142</v>
       </c>
-      <c r="E25" s="100" t="s">
+      <c r="E25" s="98" t="s">
         <v>130</v>
       </c>
-      <c r="F25" s="100" t="s">
+      <c r="F25" s="98" t="s">
         <v>143</v>
       </c>
-      <c r="G25" s="100" t="s">
+      <c r="G25" s="98" t="s">
         <v>144</v>
       </c>
-      <c r="H25" s="100">
+      <c r="H25" s="98">
         <v>6000004401</v>
       </c>
       <c r="I25" s="38" t="s">
         <v>145</v>
       </c>
-      <c r="J25" s="103" t="s">
+      <c r="J25" s="109" t="s">
         <v>146</v>
       </c>
       <c r="K25" s="56">
         <f>0.9*86.14</f>
         <v>77.525999999999996</v>
       </c>
-      <c r="L25" s="113">
+      <c r="L25" s="100">
         <f>K25+K26</f>
         <v>142.9924</v>
       </c>
       <c r="M25" s="61"/>
-      <c r="N25" s="95" t="s">
+      <c r="N25" s="92" t="s">
         <v>95</v>
       </c>
-      <c r="O25" s="95" t="s">
+      <c r="O25" s="92" t="s">
         <v>135</v>
       </c>
-      <c r="P25" s="103" t="s">
+      <c r="P25" s="109" t="s">
         <v>179</v>
       </c>
       <c r="Q25" s="38" t="s">
@@ -5609,7 +5609,7 @@
       <c r="R25" s="3">
         <v>100</v>
       </c>
-      <c r="S25" s="95">
+      <c r="S25" s="92">
         <f>R25+R26</f>
         <v>179</v>
       </c>
@@ -5617,105 +5617,105 @@
         <f t="shared" si="2"/>
         <v>-22.474000000000004</v>
       </c>
-      <c r="U25" s="132">
+      <c r="U25" s="93">
         <f>L25-S25</f>
         <v>-36.007599999999996</v>
       </c>
-      <c r="V25" s="117">
+      <c r="V25" s="95">
         <f>U25/590</f>
         <v>-6.1029830508474568E-2</v>
       </c>
-      <c r="W25" s="132">
+      <c r="W25" s="93">
         <f>(U25/L25)*100</f>
         <v>-25.181478176462523</v>
       </c>
-      <c r="X25" s="100" t="s">
+      <c r="X25" s="98" t="s">
         <v>149</v>
       </c>
-      <c r="Y25" s="135"/>
+      <c r="Y25" s="122"/>
     </row>
     <row r="26" spans="2:36" x14ac:dyDescent="0.35">
-      <c r="B26" s="101"/>
-      <c r="C26" s="101"/>
-      <c r="D26" s="97"/>
-      <c r="E26" s="101"/>
-      <c r="F26" s="101"/>
-      <c r="G26" s="101"/>
-      <c r="H26" s="101"/>
+      <c r="B26" s="99"/>
+      <c r="C26" s="99"/>
+      <c r="D26" s="104"/>
+      <c r="E26" s="99"/>
+      <c r="F26" s="99"/>
+      <c r="G26" s="99"/>
+      <c r="H26" s="99"/>
       <c r="I26" s="38" t="s">
         <v>150</v>
       </c>
-      <c r="J26" s="103"/>
+      <c r="J26" s="109"/>
       <c r="K26" s="56">
         <f>0.76*86.14</f>
         <v>65.466400000000007</v>
       </c>
-      <c r="L26" s="114"/>
+      <c r="L26" s="101"/>
       <c r="M26" s="61"/>
-      <c r="N26" s="95"/>
-      <c r="O26" s="95"/>
-      <c r="P26" s="103"/>
+      <c r="N26" s="92"/>
+      <c r="O26" s="92"/>
+      <c r="P26" s="109"/>
       <c r="Q26" s="38" t="s">
         <v>150</v>
       </c>
       <c r="R26" s="3">
         <v>79</v>
       </c>
-      <c r="S26" s="95"/>
+      <c r="S26" s="92"/>
       <c r="T26" s="62">
         <f t="shared" si="2"/>
         <v>-13.533599999999993</v>
       </c>
-      <c r="U26" s="134"/>
-      <c r="V26" s="118"/>
-      <c r="W26" s="134"/>
-      <c r="X26" s="101"/>
-      <c r="Y26" s="137"/>
+      <c r="U26" s="97"/>
+      <c r="V26" s="96"/>
+      <c r="W26" s="97"/>
+      <c r="X26" s="99"/>
+      <c r="Y26" s="124"/>
     </row>
     <row r="27" spans="2:36" x14ac:dyDescent="0.35">
-      <c r="B27" s="100">
+      <c r="B27" s="98">
         <v>10</v>
       </c>
-      <c r="C27" s="100" t="s">
+      <c r="C27" s="98" t="s">
         <v>13</v>
       </c>
-      <c r="D27" s="96" t="s">
+      <c r="D27" s="103" t="s">
         <v>142</v>
       </c>
-      <c r="E27" s="100" t="s">
+      <c r="E27" s="98" t="s">
         <v>130</v>
       </c>
-      <c r="F27" s="100" t="s">
+      <c r="F27" s="98" t="s">
         <v>143</v>
       </c>
-      <c r="G27" s="100" t="s">
+      <c r="G27" s="98" t="s">
         <v>144</v>
       </c>
-      <c r="H27" s="100">
+      <c r="H27" s="98">
         <v>6000004401</v>
       </c>
       <c r="I27" s="38" t="s">
         <v>180</v>
       </c>
-      <c r="J27" s="103" t="s">
+      <c r="J27" s="109" t="s">
         <v>146</v>
       </c>
       <c r="K27" s="56">
         <f>0.9*86.14</f>
         <v>77.525999999999996</v>
       </c>
-      <c r="L27" s="113">
+      <c r="L27" s="100">
         <f>K27+K28</f>
         <v>142.9924</v>
       </c>
       <c r="M27" s="61"/>
-      <c r="N27" s="95" t="s">
+      <c r="N27" s="92" t="s">
         <v>95</v>
       </c>
-      <c r="O27" s="95" t="s">
+      <c r="O27" s="92" t="s">
         <v>135</v>
       </c>
-      <c r="P27" s="103" t="s">
+      <c r="P27" s="109" t="s">
         <v>181</v>
       </c>
       <c r="Q27" s="38" t="s">
@@ -5724,7 +5724,7 @@
       <c r="R27" s="3">
         <v>96</v>
       </c>
-      <c r="S27" s="95">
+      <c r="S27" s="92">
         <f>R27+R28</f>
         <v>181</v>
       </c>
@@ -5732,104 +5732,104 @@
         <f t="shared" si="2"/>
         <v>-18.474000000000004</v>
       </c>
-      <c r="U27" s="132">
+      <c r="U27" s="93">
         <f>L27-S27</f>
         <v>-38.007599999999996</v>
       </c>
-      <c r="V27" s="117">
+      <c r="V27" s="95">
         <f>U27/590</f>
         <v>-6.4419661016949153E-2</v>
       </c>
-      <c r="W27" s="132">
+      <c r="W27" s="93">
         <f>(U27/L27)*100</f>
         <v>-26.580153910277748</v>
       </c>
-      <c r="X27" s="100" t="s">
+      <c r="X27" s="98" t="s">
         <v>149</v>
       </c>
-      <c r="Y27" s="135"/>
+      <c r="Y27" s="122"/>
     </row>
     <row r="28" spans="2:36" x14ac:dyDescent="0.35">
-      <c r="B28" s="101"/>
-      <c r="C28" s="101"/>
-      <c r="D28" s="97"/>
-      <c r="E28" s="101"/>
-      <c r="F28" s="101"/>
-      <c r="G28" s="101"/>
-      <c r="H28" s="101"/>
+      <c r="B28" s="99"/>
+      <c r="C28" s="99"/>
+      <c r="D28" s="104"/>
+      <c r="E28" s="99"/>
+      <c r="F28" s="99"/>
+      <c r="G28" s="99"/>
+      <c r="H28" s="99"/>
       <c r="I28" s="38" t="s">
         <v>182</v>
       </c>
-      <c r="J28" s="103"/>
+      <c r="J28" s="109"/>
       <c r="K28" s="56">
         <f>0.76*86.14</f>
         <v>65.466400000000007</v>
       </c>
-      <c r="L28" s="114"/>
+      <c r="L28" s="101"/>
       <c r="M28" s="61"/>
-      <c r="N28" s="95"/>
-      <c r="O28" s="95"/>
-      <c r="P28" s="103"/>
+      <c r="N28" s="92"/>
+      <c r="O28" s="92"/>
+      <c r="P28" s="109"/>
       <c r="Q28" s="38" t="s">
         <v>150</v>
       </c>
       <c r="R28" s="3">
         <v>85</v>
       </c>
-      <c r="S28" s="95"/>
+      <c r="S28" s="92"/>
       <c r="T28" s="46">
         <f t="shared" si="2"/>
         <v>-19.533599999999993</v>
       </c>
-      <c r="U28" s="134"/>
-      <c r="V28" s="118"/>
-      <c r="W28" s="134"/>
-      <c r="X28" s="101"/>
-      <c r="Y28" s="137"/>
+      <c r="U28" s="97"/>
+      <c r="V28" s="96"/>
+      <c r="W28" s="97"/>
+      <c r="X28" s="99"/>
+      <c r="Y28" s="124"/>
     </row>
     <row r="29" spans="2:36" x14ac:dyDescent="0.35">
-      <c r="B29" s="100">
+      <c r="B29" s="98">
         <v>11</v>
       </c>
-      <c r="C29" s="100" t="s">
+      <c r="C29" s="98" t="s">
         <v>13</v>
       </c>
-      <c r="D29" s="96" t="s">
+      <c r="D29" s="103" t="s">
         <v>119</v>
       </c>
-      <c r="E29" s="100" t="s">
+      <c r="E29" s="98" t="s">
         <v>130</v>
       </c>
-      <c r="F29" s="100" t="s">
+      <c r="F29" s="98" t="s">
         <v>121</v>
       </c>
-      <c r="G29" s="100" t="s">
+      <c r="G29" s="98" t="s">
         <v>183</v>
       </c>
-      <c r="H29" s="100">
+      <c r="H29" s="98">
         <v>6000004269</v>
       </c>
       <c r="I29" s="38" t="s">
         <v>123</v>
       </c>
-      <c r="J29" s="113" t="s">
+      <c r="J29" s="100" t="s">
         <v>131</v>
       </c>
       <c r="K29" s="57">
         <f>2.278*(L29/(2.278*2+1.134*2))</f>
         <v>2.7807356389214539</v>
       </c>
-      <c r="L29" s="113">
+      <c r="L29" s="100">
         <v>8.33</v>
       </c>
       <c r="M29" s="61"/>
-      <c r="N29" s="113" t="s">
+      <c r="N29" s="100" t="s">
         <v>87</v>
       </c>
-      <c r="O29" s="113" t="s">
+      <c r="O29" s="100" t="s">
         <v>130</v>
       </c>
-      <c r="P29" s="103" t="s">
+      <c r="P29" s="109" t="s">
         <v>184</v>
       </c>
       <c r="Q29" s="38" t="s">
@@ -5839,51 +5839,51 @@
         <f>2.278*(S29/(2.278*2+1.134*2))</f>
         <v>2.8875586166471283</v>
       </c>
-      <c r="S29" s="95">
+      <c r="S29" s="92">
         <v>8.65</v>
       </c>
       <c r="T29" s="46">
         <f t="shared" si="2"/>
         <v>-0.1068229777256744</v>
       </c>
-      <c r="U29" s="128">
+      <c r="U29" s="127">
         <f>L29-S29</f>
         <v>-0.32000000000000028</v>
       </c>
-      <c r="V29" s="117">
+      <c r="V29" s="95">
         <f>U29/590</f>
         <v>-5.4237288135593274E-4</v>
       </c>
-      <c r="W29" s="132">
+      <c r="W29" s="93">
         <f>(U29/L29)*100</f>
         <v>-3.8415366146458614</v>
       </c>
-      <c r="X29" s="100" t="s">
+      <c r="X29" s="98" t="s">
         <v>132</v>
       </c>
-      <c r="Y29" s="135"/>
+      <c r="Y29" s="122"/>
     </row>
     <row r="30" spans="2:36" x14ac:dyDescent="0.35">
-      <c r="B30" s="101"/>
-      <c r="C30" s="101"/>
-      <c r="D30" s="97"/>
-      <c r="E30" s="101"/>
-      <c r="F30" s="101"/>
-      <c r="G30" s="101"/>
-      <c r="H30" s="101"/>
+      <c r="B30" s="99"/>
+      <c r="C30" s="99"/>
+      <c r="D30" s="104"/>
+      <c r="E30" s="99"/>
+      <c r="F30" s="99"/>
+      <c r="G30" s="99"/>
+      <c r="H30" s="99"/>
       <c r="I30" s="38" t="s">
         <v>129</v>
       </c>
-      <c r="J30" s="114"/>
+      <c r="J30" s="101"/>
       <c r="K30" s="57">
         <f>1.134*(L29/(2.278*2+1.134*2))</f>
         <v>1.3842643610785463</v>
       </c>
-      <c r="L30" s="114"/>
+      <c r="L30" s="101"/>
       <c r="M30" s="61"/>
-      <c r="N30" s="114"/>
-      <c r="O30" s="114"/>
-      <c r="P30" s="103"/>
+      <c r="N30" s="101"/>
+      <c r="O30" s="101"/>
+      <c r="P30" s="109"/>
       <c r="Q30" s="38" t="s">
         <v>129</v>
       </c>
@@ -5891,62 +5891,62 @@
         <f>1.134*(S29/(2.278*2+1.134*2))</f>
         <v>1.4374413833528723</v>
       </c>
-      <c r="S30" s="95"/>
+      <c r="S30" s="92"/>
       <c r="T30" s="46">
         <f t="shared" si="2"/>
         <v>-5.3177022274325969E-2</v>
       </c>
-      <c r="U30" s="130"/>
-      <c r="V30" s="118"/>
-      <c r="W30" s="134"/>
-      <c r="X30" s="101"/>
-      <c r="Y30" s="137"/>
+      <c r="U30" s="94"/>
+      <c r="V30" s="96"/>
+      <c r="W30" s="97"/>
+      <c r="X30" s="99"/>
+      <c r="Y30" s="124"/>
     </row>
     <row r="31" spans="2:36" x14ac:dyDescent="0.35">
-      <c r="B31" s="100">
+      <c r="B31" s="98">
         <v>12</v>
       </c>
-      <c r="C31" s="100" t="s">
+      <c r="C31" s="98" t="s">
         <v>25</v>
       </c>
-      <c r="D31" s="100" t="s">
+      <c r="D31" s="98" t="s">
         <v>173</v>
       </c>
-      <c r="E31" s="100" t="s">
+      <c r="E31" s="98" t="s">
         <v>130</v>
       </c>
-      <c r="F31" s="100" t="s">
+      <c r="F31" s="98" t="s">
         <v>157</v>
       </c>
-      <c r="G31" s="113" t="s">
+      <c r="G31" s="100" t="s">
         <v>174</v>
       </c>
-      <c r="H31" s="100">
+      <c r="H31" s="98">
         <v>6000004458</v>
       </c>
       <c r="I31" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="J31" s="113" t="s">
+      <c r="J31" s="100" t="s">
         <v>131</v>
       </c>
       <c r="K31" s="60">
         <v>1.22</v>
       </c>
-      <c r="L31" s="113">
+      <c r="L31" s="100">
         <f>K31+K32+K33</f>
         <v>5.96</v>
       </c>
-      <c r="M31" s="142">
+      <c r="M31" s="105">
         <v>45824</v>
       </c>
-      <c r="N31" s="113" t="s">
+      <c r="N31" s="100" t="s">
         <v>25</v>
       </c>
-      <c r="O31" s="107" t="s">
+      <c r="O31" s="106" t="s">
         <v>130</v>
       </c>
-      <c r="P31" s="103" t="s">
+      <c r="P31" s="109" t="s">
         <v>185</v>
       </c>
       <c r="Q31" s="38" t="s">
@@ -5955,7 +5955,7 @@
       <c r="R31" s="3">
         <v>1.25</v>
       </c>
-      <c r="S31" s="100">
+      <c r="S31" s="98">
         <f>R31+R32+R33</f>
         <v>6.25</v>
       </c>
@@ -5963,143 +5963,143 @@
         <f t="shared" si="2"/>
         <v>-3.0000000000000027E-2</v>
       </c>
-      <c r="U31" s="128">
+      <c r="U31" s="127">
         <f>L31-S31</f>
         <v>-0.29000000000000004</v>
       </c>
-      <c r="V31" s="139">
+      <c r="V31" s="107">
         <f>U31/590</f>
         <v>-4.9152542372881357E-4</v>
       </c>
-      <c r="W31" s="132">
+      <c r="W31" s="93">
         <f>(U31/L31)*100</f>
         <v>-4.8657718120805376</v>
       </c>
-      <c r="X31" s="100" t="s">
+      <c r="X31" s="98" t="s">
         <v>132</v>
       </c>
-      <c r="Y31" s="135"/>
+      <c r="Y31" s="122"/>
     </row>
     <row r="32" spans="2:36" x14ac:dyDescent="0.35">
-      <c r="B32" s="119"/>
-      <c r="C32" s="119"/>
-      <c r="D32" s="119"/>
-      <c r="E32" s="119"/>
-      <c r="F32" s="119"/>
-      <c r="G32" s="126"/>
-      <c r="H32" s="119"/>
+      <c r="B32" s="121"/>
+      <c r="C32" s="121"/>
+      <c r="D32" s="121"/>
+      <c r="E32" s="121"/>
+      <c r="F32" s="121"/>
+      <c r="G32" s="125"/>
+      <c r="H32" s="121"/>
       <c r="I32" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="J32" s="126"/>
+      <c r="J32" s="125"/>
       <c r="K32" s="60">
         <v>2.37</v>
       </c>
-      <c r="L32" s="126"/>
-      <c r="M32" s="142"/>
-      <c r="N32" s="126"/>
-      <c r="O32" s="107"/>
-      <c r="P32" s="103"/>
+      <c r="L32" s="125"/>
+      <c r="M32" s="105"/>
+      <c r="N32" s="125"/>
+      <c r="O32" s="106"/>
+      <c r="P32" s="109"/>
       <c r="Q32" s="38" t="s">
         <v>162</v>
       </c>
       <c r="R32" s="3">
         <v>2.5</v>
       </c>
-      <c r="S32" s="119"/>
+      <c r="S32" s="121"/>
       <c r="T32" s="49">
         <f t="shared" si="2"/>
         <v>-0.12999999999999989</v>
       </c>
-      <c r="U32" s="129"/>
-      <c r="V32" s="140"/>
-      <c r="W32" s="133"/>
-      <c r="X32" s="119"/>
-      <c r="Y32" s="136"/>
+      <c r="U32" s="128"/>
+      <c r="V32" s="134"/>
+      <c r="W32" s="120"/>
+      <c r="X32" s="121"/>
+      <c r="Y32" s="123"/>
     </row>
     <row r="33" spans="2:25" x14ac:dyDescent="0.35">
-      <c r="B33" s="101"/>
-      <c r="C33" s="101"/>
-      <c r="D33" s="101"/>
-      <c r="E33" s="101"/>
-      <c r="F33" s="101"/>
-      <c r="G33" s="114"/>
-      <c r="H33" s="101"/>
+      <c r="B33" s="99"/>
+      <c r="C33" s="99"/>
+      <c r="D33" s="99"/>
+      <c r="E33" s="99"/>
+      <c r="F33" s="99"/>
+      <c r="G33" s="101"/>
+      <c r="H33" s="99"/>
       <c r="I33" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="J33" s="114"/>
+      <c r="J33" s="101"/>
       <c r="K33" s="60">
         <v>2.37</v>
       </c>
-      <c r="L33" s="114"/>
-      <c r="M33" s="142"/>
-      <c r="N33" s="114"/>
-      <c r="O33" s="107"/>
-      <c r="P33" s="103"/>
+      <c r="L33" s="101"/>
+      <c r="M33" s="105"/>
+      <c r="N33" s="101"/>
+      <c r="O33" s="106"/>
+      <c r="P33" s="109"/>
       <c r="Q33" s="38" t="s">
         <v>164</v>
       </c>
       <c r="R33" s="3">
         <v>2.5</v>
       </c>
-      <c r="S33" s="101"/>
+      <c r="S33" s="99"/>
       <c r="T33" s="49">
         <f t="shared" si="2"/>
         <v>-0.12999999999999989</v>
       </c>
-      <c r="U33" s="130"/>
-      <c r="V33" s="141"/>
-      <c r="W33" s="134"/>
-      <c r="X33" s="101"/>
-      <c r="Y33" s="137"/>
+      <c r="U33" s="94"/>
+      <c r="V33" s="108"/>
+      <c r="W33" s="97"/>
+      <c r="X33" s="99"/>
+      <c r="Y33" s="124"/>
     </row>
     <row r="34" spans="2:25" x14ac:dyDescent="0.35">
-      <c r="B34" s="100">
+      <c r="B34" s="98">
         <v>13</v>
       </c>
-      <c r="C34" s="100" t="s">
+      <c r="C34" s="98" t="s">
         <v>186</v>
       </c>
-      <c r="D34" s="96" t="s">
+      <c r="D34" s="103" t="s">
         <v>142</v>
       </c>
-      <c r="E34" s="100" t="s">
+      <c r="E34" s="98" t="s">
         <v>130</v>
       </c>
-      <c r="F34" s="100" t="s">
+      <c r="F34" s="98" t="s">
         <v>143</v>
       </c>
-      <c r="G34" s="100" t="s">
+      <c r="G34" s="98" t="s">
         <v>187</v>
       </c>
-      <c r="H34" s="100">
+      <c r="H34" s="98">
         <v>6000004383</v>
       </c>
       <c r="I34" s="38" t="s">
         <v>145</v>
       </c>
-      <c r="J34" s="103" t="s">
+      <c r="J34" s="109" t="s">
         <v>146</v>
       </c>
       <c r="K34" s="56">
         <f>0.9*86.14</f>
         <v>77.525999999999996</v>
       </c>
-      <c r="L34" s="138">
+      <c r="L34" s="102">
         <f>K34+K35</f>
         <v>142.9924</v>
       </c>
-      <c r="M34" s="142">
+      <c r="M34" s="105">
         <v>45853</v>
       </c>
-      <c r="N34" s="95" t="s">
+      <c r="N34" s="92" t="s">
         <v>95</v>
       </c>
-      <c r="O34" s="107" t="s">
+      <c r="O34" s="106" t="s">
         <v>130</v>
       </c>
-      <c r="P34" s="103" t="s">
+      <c r="P34" s="109" t="s">
         <v>188</v>
       </c>
       <c r="Q34" s="38" t="s">
@@ -6108,7 +6108,7 @@
       <c r="R34" s="3">
         <v>90</v>
       </c>
-      <c r="S34" s="95">
+      <c r="S34" s="92">
         <f>R34+R35</f>
         <v>165</v>
       </c>
@@ -6116,107 +6116,107 @@
         <f t="shared" si="2"/>
         <v>-12.474000000000004</v>
       </c>
-      <c r="U34" s="132">
+      <c r="U34" s="93">
         <f>L34-S34</f>
         <v>-22.007599999999996</v>
       </c>
-      <c r="V34" s="132">
+      <c r="V34" s="93">
         <f>U34/590</f>
         <v>-3.7301016949152534E-2</v>
       </c>
-      <c r="W34" s="132">
+      <c r="W34" s="93">
         <f>(U34/L34)*100</f>
         <v>-15.390748039755955</v>
       </c>
-      <c r="X34" s="100" t="s">
+      <c r="X34" s="98" t="s">
         <v>149</v>
       </c>
-      <c r="Y34" s="135"/>
+      <c r="Y34" s="122"/>
     </row>
     <row r="35" spans="2:25" x14ac:dyDescent="0.35">
-      <c r="B35" s="101"/>
-      <c r="C35" s="101"/>
-      <c r="D35" s="97"/>
-      <c r="E35" s="101"/>
-      <c r="F35" s="101"/>
-      <c r="G35" s="101"/>
-      <c r="H35" s="101"/>
+      <c r="B35" s="99"/>
+      <c r="C35" s="99"/>
+      <c r="D35" s="104"/>
+      <c r="E35" s="99"/>
+      <c r="F35" s="99"/>
+      <c r="G35" s="99"/>
+      <c r="H35" s="99"/>
       <c r="I35" s="38" t="s">
         <v>150</v>
       </c>
-      <c r="J35" s="103"/>
+      <c r="J35" s="109"/>
       <c r="K35" s="56">
         <f>0.76*86.14</f>
         <v>65.466400000000007</v>
       </c>
-      <c r="L35" s="114"/>
-      <c r="M35" s="142"/>
-      <c r="N35" s="95"/>
-      <c r="O35" s="107"/>
-      <c r="P35" s="103"/>
+      <c r="L35" s="101"/>
+      <c r="M35" s="105"/>
+      <c r="N35" s="92"/>
+      <c r="O35" s="106"/>
+      <c r="P35" s="109"/>
       <c r="Q35" s="38" t="s">
         <v>150</v>
       </c>
       <c r="R35" s="3">
         <v>75</v>
       </c>
-      <c r="S35" s="95"/>
+      <c r="S35" s="92"/>
       <c r="T35" s="46">
         <f t="shared" si="2"/>
         <v>-9.5335999999999927</v>
       </c>
-      <c r="U35" s="130"/>
-      <c r="V35" s="134"/>
-      <c r="W35" s="134"/>
-      <c r="X35" s="101"/>
-      <c r="Y35" s="137"/>
+      <c r="U35" s="94"/>
+      <c r="V35" s="97"/>
+      <c r="W35" s="97"/>
+      <c r="X35" s="99"/>
+      <c r="Y35" s="124"/>
     </row>
     <row r="36" spans="2:25" x14ac:dyDescent="0.35">
-      <c r="B36" s="100">
+      <c r="B36" s="98">
         <v>14</v>
       </c>
-      <c r="C36" s="100" t="s">
+      <c r="C36" s="98" t="s">
         <v>13</v>
       </c>
-      <c r="D36" s="96" t="s">
+      <c r="D36" s="103" t="s">
         <v>119</v>
       </c>
-      <c r="E36" s="100" t="s">
+      <c r="E36" s="98" t="s">
         <v>130</v>
       </c>
-      <c r="F36" s="100" t="s">
+      <c r="F36" s="98" t="s">
         <v>121</v>
       </c>
-      <c r="G36" s="100" t="s">
+      <c r="G36" s="98" t="s">
         <v>183</v>
       </c>
-      <c r="H36" s="100">
+      <c r="H36" s="98">
         <v>6000004269</v>
       </c>
       <c r="I36" s="38" t="s">
         <v>123</v>
       </c>
-      <c r="J36" s="103" t="s">
+      <c r="J36" s="109" t="s">
         <v>146</v>
       </c>
       <c r="K36" s="57">
         <f>K29*86.14</f>
         <v>239.53256793669405</v>
       </c>
-      <c r="L36" s="113">
+      <c r="L36" s="100">
         <f>L29*86.14</f>
         <v>717.5462</v>
       </c>
-      <c r="M36" s="142">
+      <c r="M36" s="105">
         <v>45853</v>
       </c>
-      <c r="N36" s="95" t="s">
+      <c r="N36" s="92" t="s">
         <v>95</v>
       </c>
-      <c r="O36" s="107" t="s">
+      <c r="O36" s="106" t="s">
         <v>130</v>
       </c>
-      <c r="P36" s="95" t="s">
+      <c r="P36" s="92" t="s">
         <v>189</v>
       </c>
       <c r="Q36" s="38" t="s">
@@ -6226,51 +6226,51 @@
         <f>2.278*(S36/(2.278*2+1.134*2))</f>
         <v>282.07942555685815</v>
       </c>
-      <c r="S36" s="100">
+      <c r="S36" s="98">
         <v>845</v>
       </c>
       <c r="T36" s="46">
         <f t="shared" si="2"/>
         <v>-42.546857620164104</v>
       </c>
-      <c r="U36" s="132">
+      <c r="U36" s="93">
         <f>L36-S36</f>
         <v>-127.4538</v>
       </c>
-      <c r="V36" s="132">
+      <c r="V36" s="93">
         <f>U36/590</f>
         <v>-0.21602338983050848</v>
       </c>
-      <c r="W36" s="132">
+      <c r="W36" s="93">
         <f>(U36/L36)*100</f>
         <v>-17.762452090192937</v>
       </c>
-      <c r="X36" s="100" t="s">
+      <c r="X36" s="98" t="s">
         <v>149</v>
       </c>
-      <c r="Y36" s="135"/>
+      <c r="Y36" s="122"/>
     </row>
     <row r="37" spans="2:25" x14ac:dyDescent="0.35">
-      <c r="B37" s="101"/>
-      <c r="C37" s="101"/>
-      <c r="D37" s="97"/>
-      <c r="E37" s="101"/>
-      <c r="F37" s="101"/>
-      <c r="G37" s="101"/>
-      <c r="H37" s="101"/>
+      <c r="B37" s="99"/>
+      <c r="C37" s="99"/>
+      <c r="D37" s="104"/>
+      <c r="E37" s="99"/>
+      <c r="F37" s="99"/>
+      <c r="G37" s="99"/>
+      <c r="H37" s="99"/>
       <c r="I37" s="38" t="s">
         <v>129</v>
       </c>
-      <c r="J37" s="103"/>
+      <c r="J37" s="109"/>
       <c r="K37" s="57">
         <f>K30*86.14</f>
         <v>119.24053206330598</v>
       </c>
-      <c r="L37" s="114"/>
-      <c r="M37" s="142"/>
-      <c r="N37" s="95"/>
-      <c r="O37" s="107"/>
-      <c r="P37" s="95"/>
+      <c r="L37" s="101"/>
+      <c r="M37" s="105"/>
+      <c r="N37" s="92"/>
+      <c r="O37" s="106"/>
+      <c r="P37" s="92"/>
       <c r="Q37" s="38" t="s">
         <v>129</v>
       </c>
@@ -6278,63 +6278,63 @@
         <f>1.134*(S36/(2.278*2+1.134*2))</f>
         <v>140.42057444314185</v>
       </c>
-      <c r="S37" s="101"/>
+      <c r="S37" s="99"/>
       <c r="T37" s="46">
         <f t="shared" si="2"/>
         <v>-21.180042379835868</v>
       </c>
-      <c r="U37" s="134"/>
-      <c r="V37" s="134"/>
-      <c r="W37" s="134"/>
-      <c r="X37" s="101"/>
-      <c r="Y37" s="137"/>
+      <c r="U37" s="97"/>
+      <c r="V37" s="97"/>
+      <c r="W37" s="97"/>
+      <c r="X37" s="99"/>
+      <c r="Y37" s="124"/>
     </row>
     <row r="38" spans="2:25" ht="29" x14ac:dyDescent="0.35">
-      <c r="B38" s="100">
+      <c r="B38" s="98">
         <v>15</v>
       </c>
-      <c r="C38" s="100" t="s">
+      <c r="C38" s="98" t="s">
         <v>57</v>
       </c>
-      <c r="D38" s="100" t="s">
+      <c r="D38" s="98" t="s">
         <v>171</v>
       </c>
-      <c r="E38" s="100" t="s">
+      <c r="E38" s="98" t="s">
         <v>130</v>
       </c>
-      <c r="F38" s="100" t="s">
+      <c r="F38" s="98" t="s">
         <v>121</v>
       </c>
-      <c r="G38" s="100" t="s">
+      <c r="G38" s="98" t="s">
         <v>190</v>
       </c>
-      <c r="H38" s="100">
+      <c r="H38" s="98">
         <v>6000004325</v>
       </c>
       <c r="I38" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="J38" s="113" t="s">
+      <c r="J38" s="100" t="s">
         <v>146</v>
       </c>
       <c r="K38" s="5">
         <f>7.1*86.14</f>
         <v>611.59399999999994</v>
       </c>
-      <c r="L38" s="113">
+      <c r="L38" s="100">
         <f>K38+K39</f>
         <v>1227.4949999999999</v>
       </c>
-      <c r="M38" s="142">
+      <c r="M38" s="105">
         <v>45853</v>
       </c>
-      <c r="N38" s="143" t="s">
+      <c r="N38" s="132" t="s">
         <v>95</v>
       </c>
-      <c r="O38" s="107" t="s">
+      <c r="O38" s="106" t="s">
         <v>130</v>
       </c>
-      <c r="P38" s="95" t="s">
+      <c r="P38" s="92" t="s">
         <v>192</v>
       </c>
       <c r="Q38" s="38" t="s">
@@ -6343,7 +6343,7 @@
       <c r="R38" s="3">
         <v>845</v>
       </c>
-      <c r="S38" s="95">
+      <c r="S38" s="92">
         <f>R38+R39</f>
         <v>1715</v>
       </c>
@@ -6351,107 +6351,107 @@
         <f t="shared" si="2"/>
         <v>-233.40600000000006</v>
       </c>
-      <c r="U38" s="132">
+      <c r="U38" s="93">
         <f>L38-S38</f>
         <v>-487.50500000000011</v>
       </c>
-      <c r="V38" s="132">
+      <c r="V38" s="93">
         <f>U38/590</f>
         <v>-0.82627966101694938</v>
       </c>
-      <c r="W38" s="132">
+      <c r="W38" s="93">
         <f>(U38/L38)*100</f>
         <v>-39.715436722756522</v>
       </c>
-      <c r="X38" s="100" t="s">
+      <c r="X38" s="98" t="s">
         <v>149</v>
       </c>
-      <c r="Y38" s="135"/>
+      <c r="Y38" s="122"/>
     </row>
     <row r="39" spans="2:25" ht="29" x14ac:dyDescent="0.35">
-      <c r="B39" s="101"/>
-      <c r="C39" s="101"/>
-      <c r="D39" s="101"/>
-      <c r="E39" s="101"/>
-      <c r="F39" s="101"/>
-      <c r="G39" s="101"/>
-      <c r="H39" s="101"/>
+      <c r="B39" s="99"/>
+      <c r="C39" s="99"/>
+      <c r="D39" s="99"/>
+      <c r="E39" s="99"/>
+      <c r="F39" s="99"/>
+      <c r="G39" s="99"/>
+      <c r="H39" s="99"/>
       <c r="I39" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="J39" s="114"/>
+      <c r="J39" s="101"/>
       <c r="K39" s="5">
         <f>7.15*86.14</f>
         <v>615.90100000000007</v>
       </c>
-      <c r="L39" s="114"/>
-      <c r="M39" s="142"/>
-      <c r="N39" s="144"/>
-      <c r="O39" s="107"/>
-      <c r="P39" s="95"/>
+      <c r="L39" s="101"/>
+      <c r="M39" s="105"/>
+      <c r="N39" s="133"/>
+      <c r="O39" s="106"/>
+      <c r="P39" s="92"/>
       <c r="Q39" s="38" t="s">
         <v>195</v>
       </c>
       <c r="R39" s="3">
         <v>870</v>
       </c>
-      <c r="S39" s="95"/>
+      <c r="S39" s="92"/>
       <c r="T39" s="57">
         <f t="shared" si="2"/>
         <v>-254.09899999999993</v>
       </c>
-      <c r="U39" s="134"/>
-      <c r="V39" s="134"/>
-      <c r="W39" s="134"/>
-      <c r="X39" s="101"/>
-      <c r="Y39" s="137"/>
+      <c r="U39" s="97"/>
+      <c r="V39" s="97"/>
+      <c r="W39" s="97"/>
+      <c r="X39" s="99"/>
+      <c r="Y39" s="124"/>
     </row>
     <row r="40" spans="2:25" x14ac:dyDescent="0.35">
-      <c r="B40" s="100">
+      <c r="B40" s="98">
         <v>16</v>
       </c>
-      <c r="C40" s="100" t="s">
+      <c r="C40" s="98" t="s">
         <v>186</v>
       </c>
-      <c r="D40" s="96" t="s">
+      <c r="D40" s="103" t="s">
         <v>142</v>
       </c>
-      <c r="E40" s="100" t="s">
+      <c r="E40" s="98" t="s">
         <v>130</v>
       </c>
-      <c r="F40" s="100" t="s">
+      <c r="F40" s="98" t="s">
         <v>143</v>
       </c>
-      <c r="G40" s="100" t="s">
+      <c r="G40" s="98" t="s">
         <v>187</v>
       </c>
-      <c r="H40" s="100">
+      <c r="H40" s="98">
         <v>6000004382</v>
       </c>
       <c r="I40" s="38" t="s">
         <v>196</v>
       </c>
-      <c r="J40" s="103" t="s">
+      <c r="J40" s="109" t="s">
         <v>146</v>
       </c>
       <c r="K40" s="56">
         <f>0.9*86.14</f>
         <v>77.525999999999996</v>
       </c>
-      <c r="L40" s="138">
+      <c r="L40" s="102">
         <f>K40+K41</f>
         <v>142.9924</v>
       </c>
-      <c r="M40" s="142">
+      <c r="M40" s="105">
         <v>45853</v>
       </c>
-      <c r="N40" s="95" t="s">
+      <c r="N40" s="92" t="s">
         <v>95</v>
       </c>
-      <c r="O40" s="107" t="s">
+      <c r="O40" s="106" t="s">
         <v>130</v>
       </c>
-      <c r="P40" s="95" t="s">
+      <c r="P40" s="92" t="s">
         <v>197</v>
       </c>
       <c r="Q40" s="38" t="s">
@@ -6460,7 +6460,7 @@
       <c r="R40" s="3">
         <v>90</v>
       </c>
-      <c r="S40" s="95">
+      <c r="S40" s="92">
         <f>R40+R41</f>
         <v>175</v>
       </c>
@@ -6468,107 +6468,107 @@
         <f t="shared" si="2"/>
         <v>-12.474000000000004</v>
       </c>
-      <c r="U40" s="132">
+      <c r="U40" s="93">
         <f>L40-S40</f>
         <v>-32.007599999999996</v>
       </c>
-      <c r="V40" s="132">
+      <c r="V40" s="93">
         <f>U40/590</f>
         <v>-5.4250169491525418E-2</v>
       </c>
-      <c r="W40" s="117">
+      <c r="W40" s="95">
         <f>(U40/L40)*100</f>
         <v>-22.384126708832074</v>
       </c>
-      <c r="X40" s="100" t="s">
+      <c r="X40" s="98" t="s">
         <v>149</v>
       </c>
-      <c r="Y40" s="135"/>
+      <c r="Y40" s="122"/>
     </row>
     <row r="41" spans="2:25" x14ac:dyDescent="0.35">
-      <c r="B41" s="101"/>
-      <c r="C41" s="101"/>
-      <c r="D41" s="97"/>
-      <c r="E41" s="101"/>
-      <c r="F41" s="101"/>
-      <c r="G41" s="101"/>
-      <c r="H41" s="101"/>
+      <c r="B41" s="99"/>
+      <c r="C41" s="99"/>
+      <c r="D41" s="104"/>
+      <c r="E41" s="99"/>
+      <c r="F41" s="99"/>
+      <c r="G41" s="99"/>
+      <c r="H41" s="99"/>
       <c r="I41" s="38" t="s">
         <v>198</v>
       </c>
-      <c r="J41" s="103"/>
+      <c r="J41" s="109"/>
       <c r="K41" s="56">
         <f>0.76*86.14</f>
         <v>65.466400000000007</v>
       </c>
-      <c r="L41" s="114"/>
-      <c r="M41" s="142"/>
-      <c r="N41" s="95"/>
-      <c r="O41" s="107"/>
-      <c r="P41" s="95"/>
+      <c r="L41" s="101"/>
+      <c r="M41" s="105"/>
+      <c r="N41" s="92"/>
+      <c r="O41" s="106"/>
+      <c r="P41" s="92"/>
       <c r="Q41" s="38" t="s">
         <v>150</v>
       </c>
       <c r="R41" s="3">
         <v>85</v>
       </c>
-      <c r="S41" s="95"/>
+      <c r="S41" s="92"/>
       <c r="T41" s="46">
         <f t="shared" si="2"/>
         <v>-19.533599999999993</v>
       </c>
-      <c r="U41" s="130"/>
-      <c r="V41" s="134"/>
-      <c r="W41" s="118"/>
-      <c r="X41" s="101"/>
-      <c r="Y41" s="137"/>
+      <c r="U41" s="94"/>
+      <c r="V41" s="97"/>
+      <c r="W41" s="96"/>
+      <c r="X41" s="99"/>
+      <c r="Y41" s="124"/>
     </row>
     <row r="42" spans="2:25" x14ac:dyDescent="0.35">
-      <c r="B42" s="100">
+      <c r="B42" s="98">
         <v>17</v>
       </c>
-      <c r="C42" s="100" t="s">
+      <c r="C42" s="98" t="s">
         <v>186</v>
       </c>
-      <c r="D42" s="96" t="s">
+      <c r="D42" s="103" t="s">
         <v>142</v>
       </c>
-      <c r="E42" s="100" t="s">
+      <c r="E42" s="98" t="s">
         <v>130</v>
       </c>
-      <c r="F42" s="100" t="s">
+      <c r="F42" s="98" t="s">
         <v>143</v>
       </c>
-      <c r="G42" s="100" t="s">
+      <c r="G42" s="98" t="s">
         <v>187</v>
       </c>
-      <c r="H42" s="100">
+      <c r="H42" s="98">
         <v>6000004383</v>
       </c>
       <c r="I42" s="38" t="s">
         <v>145</v>
       </c>
-      <c r="J42" s="113" t="s">
+      <c r="J42" s="100" t="s">
         <v>131</v>
       </c>
       <c r="K42" s="56">
         <f>0.9</f>
         <v>0.9</v>
       </c>
-      <c r="L42" s="138">
+      <c r="L42" s="102">
         <f>K42+K43</f>
         <v>1.6600000000000001</v>
       </c>
-      <c r="M42" s="142">
+      <c r="M42" s="105">
         <v>45853</v>
       </c>
-      <c r="N42" s="95" t="s">
+      <c r="N42" s="92" t="s">
         <v>25</v>
       </c>
-      <c r="O42" s="107" t="s">
+      <c r="O42" s="106" t="s">
         <v>130</v>
       </c>
-      <c r="P42" s="95" t="s">
+      <c r="P42" s="92" t="s">
         <v>199</v>
       </c>
       <c r="Q42" s="38" t="s">
@@ -6577,7 +6577,7 @@
       <c r="R42" s="3">
         <v>0.76</v>
       </c>
-      <c r="S42" s="95">
+      <c r="S42" s="92">
         <f>R42+R43</f>
         <v>1.4100000000000001</v>
       </c>
@@ -6585,105 +6585,105 @@
         <f t="shared" si="2"/>
         <v>0.14000000000000001</v>
       </c>
-      <c r="U42" s="132">
+      <c r="U42" s="93">
         <f>L42-S42</f>
         <v>0.25</v>
       </c>
-      <c r="V42" s="139">
+      <c r="V42" s="107">
         <f>U42/590</f>
         <v>4.2372881355932202E-4</v>
       </c>
-      <c r="W42" s="117">
+      <c r="W42" s="95">
         <f>(V42/L42)*100</f>
         <v>2.5525832142127829E-2</v>
       </c>
-      <c r="X42" s="100" t="s">
+      <c r="X42" s="98" t="s">
         <v>132</v>
       </c>
-      <c r="Y42" s="135"/>
+      <c r="Y42" s="122"/>
     </row>
     <row r="43" spans="2:25" x14ac:dyDescent="0.35">
-      <c r="B43" s="101"/>
-      <c r="C43" s="101"/>
-      <c r="D43" s="97"/>
-      <c r="E43" s="101"/>
-      <c r="F43" s="101"/>
-      <c r="G43" s="101"/>
-      <c r="H43" s="101"/>
+      <c r="B43" s="99"/>
+      <c r="C43" s="99"/>
+      <c r="D43" s="104"/>
+      <c r="E43" s="99"/>
+      <c r="F43" s="99"/>
+      <c r="G43" s="99"/>
+      <c r="H43" s="99"/>
       <c r="I43" s="38" t="s">
         <v>150</v>
       </c>
-      <c r="J43" s="114"/>
+      <c r="J43" s="101"/>
       <c r="K43" s="56">
         <f>0.76</f>
         <v>0.76</v>
       </c>
-      <c r="L43" s="114"/>
-      <c r="M43" s="142"/>
-      <c r="N43" s="95"/>
-      <c r="O43" s="107"/>
-      <c r="P43" s="95"/>
+      <c r="L43" s="101"/>
+      <c r="M43" s="105"/>
+      <c r="N43" s="92"/>
+      <c r="O43" s="106"/>
+      <c r="P43" s="92"/>
       <c r="Q43" s="38" t="s">
         <v>150</v>
       </c>
       <c r="R43" s="3">
         <v>0.65</v>
       </c>
-      <c r="S43" s="95"/>
+      <c r="S43" s="92"/>
       <c r="T43" s="57">
         <f>K42-R43</f>
         <v>0.25</v>
       </c>
-      <c r="U43" s="130"/>
-      <c r="V43" s="141"/>
-      <c r="W43" s="118"/>
-      <c r="X43" s="101"/>
-      <c r="Y43" s="137"/>
+      <c r="U43" s="94"/>
+      <c r="V43" s="108"/>
+      <c r="W43" s="96"/>
+      <c r="X43" s="99"/>
+      <c r="Y43" s="124"/>
     </row>
     <row r="44" spans="2:25" x14ac:dyDescent="0.35">
-      <c r="B44" s="100">
+      <c r="B44" s="98">
         <v>18</v>
       </c>
-      <c r="C44" s="100" t="s">
+      <c r="C44" s="98" t="s">
         <v>186</v>
       </c>
-      <c r="D44" s="96" t="s">
+      <c r="D44" s="103" t="s">
         <v>142</v>
       </c>
-      <c r="E44" s="100" t="s">
+      <c r="E44" s="98" t="s">
         <v>130</v>
       </c>
-      <c r="F44" s="100" t="s">
+      <c r="F44" s="98" t="s">
         <v>143</v>
       </c>
-      <c r="G44" s="100" t="s">
+      <c r="G44" s="98" t="s">
         <v>187</v>
       </c>
-      <c r="H44" s="100">
+      <c r="H44" s="98">
         <v>6000004384</v>
       </c>
       <c r="I44" s="38" t="s">
         <v>180</v>
       </c>
-      <c r="J44" s="113" t="s">
+      <c r="J44" s="100" t="s">
         <v>131</v>
       </c>
       <c r="K44" s="56">
         <f>0.9</f>
         <v>0.9</v>
       </c>
-      <c r="L44" s="138">
+      <c r="L44" s="102">
         <f>K44+K45</f>
         <v>1.6600000000000001</v>
       </c>
       <c r="M44" s="61"/>
-      <c r="N44" s="113" t="s">
+      <c r="N44" s="100" t="s">
         <v>57</v>
       </c>
-      <c r="O44" s="113" t="s">
+      <c r="O44" s="100" t="s">
         <v>130</v>
       </c>
-      <c r="P44" s="95" t="s">
+      <c r="P44" s="92" t="s">
         <v>200</v>
       </c>
       <c r="Q44" s="38" t="s">
@@ -6692,7 +6692,7 @@
       <c r="R44" s="3">
         <v>0.78</v>
       </c>
-      <c r="S44" s="95">
+      <c r="S44" s="92">
         <f>R44+R45</f>
         <v>1.47</v>
       </c>
@@ -6700,104 +6700,104 @@
         <f>K44-R44</f>
         <v>0.12</v>
       </c>
-      <c r="U44" s="132">
+      <c r="U44" s="93">
         <f>L44-S44</f>
         <v>0.19000000000000017</v>
       </c>
-      <c r="V44" s="117">
+      <c r="V44" s="95">
         <f>U44/590</f>
         <v>3.2203389830508505E-4</v>
       </c>
-      <c r="W44" s="132">
+      <c r="W44" s="93">
         <f>(U44/L44)*100</f>
         <v>11.44578313253013</v>
       </c>
-      <c r="X44" s="100" t="s">
+      <c r="X44" s="98" t="s">
         <v>132</v>
       </c>
-      <c r="Y44" s="135"/>
+      <c r="Y44" s="122"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.35">
-      <c r="B45" s="101"/>
-      <c r="C45" s="101"/>
-      <c r="D45" s="97"/>
-      <c r="E45" s="101"/>
-      <c r="F45" s="101"/>
-      <c r="G45" s="101"/>
-      <c r="H45" s="101"/>
+      <c r="B45" s="99"/>
+      <c r="C45" s="99"/>
+      <c r="D45" s="104"/>
+      <c r="E45" s="99"/>
+      <c r="F45" s="99"/>
+      <c r="G45" s="99"/>
+      <c r="H45" s="99"/>
       <c r="I45" s="38" t="s">
         <v>182</v>
       </c>
-      <c r="J45" s="114"/>
+      <c r="J45" s="101"/>
       <c r="K45" s="56">
         <f>0.76</f>
         <v>0.76</v>
       </c>
-      <c r="L45" s="114"/>
+      <c r="L45" s="101"/>
       <c r="M45" s="61"/>
-      <c r="N45" s="114"/>
-      <c r="O45" s="114"/>
-      <c r="P45" s="95"/>
+      <c r="N45" s="101"/>
+      <c r="O45" s="101"/>
+      <c r="P45" s="92"/>
       <c r="Q45" s="38" t="s">
         <v>150</v>
       </c>
       <c r="R45" s="3">
         <v>0.69</v>
       </c>
-      <c r="S45" s="95"/>
+      <c r="S45" s="92"/>
       <c r="T45" s="57">
         <f t="shared" ref="T45:T51" si="3">K45-R45</f>
         <v>7.0000000000000062E-2</v>
       </c>
-      <c r="U45" s="130"/>
-      <c r="V45" s="118"/>
-      <c r="W45" s="134"/>
-      <c r="X45" s="101"/>
-      <c r="Y45" s="137"/>
+      <c r="U45" s="94"/>
+      <c r="V45" s="96"/>
+      <c r="W45" s="97"/>
+      <c r="X45" s="99"/>
+      <c r="Y45" s="124"/>
     </row>
     <row r="46" spans="2:25" x14ac:dyDescent="0.35">
-      <c r="B46" s="100">
+      <c r="B46" s="98">
         <v>19</v>
       </c>
-      <c r="C46" s="100" t="s">
+      <c r="C46" s="98" t="s">
         <v>25</v>
       </c>
-      <c r="D46" s="100" t="s">
+      <c r="D46" s="98" t="s">
         <v>173</v>
       </c>
-      <c r="E46" s="100" t="s">
+      <c r="E46" s="98" t="s">
         <v>130</v>
       </c>
-      <c r="F46" s="100" t="s">
+      <c r="F46" s="98" t="s">
         <v>157</v>
       </c>
-      <c r="G46" s="113" t="s">
+      <c r="G46" s="100" t="s">
         <v>174</v>
       </c>
-      <c r="H46" s="100">
+      <c r="H46" s="98">
         <v>6000004458</v>
       </c>
       <c r="I46" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="J46" s="113" t="s">
+      <c r="J46" s="100" t="s">
         <v>131</v>
       </c>
       <c r="K46" s="60">
         <v>1.22</v>
       </c>
-      <c r="L46" s="113">
+      <c r="L46" s="100">
         <f>K46+K47+K48</f>
         <v>5.96</v>
       </c>
       <c r="M46" s="61"/>
-      <c r="N46" s="100" t="s">
+      <c r="N46" s="98" t="s">
         <v>25</v>
       </c>
-      <c r="O46" s="100" t="s">
+      <c r="O46" s="98" t="s">
         <v>130</v>
       </c>
-      <c r="P46" s="95" t="s">
+      <c r="P46" s="92" t="s">
         <v>91</v>
       </c>
       <c r="Q46" s="38" t="s">
@@ -6806,7 +6806,7 @@
       <c r="R46" s="3">
         <v>1.25</v>
       </c>
-      <c r="S46" s="100">
+      <c r="S46" s="98">
         <f>R46+R47+R48</f>
         <v>5.91</v>
       </c>
@@ -6814,141 +6814,141 @@
         <f t="shared" si="3"/>
         <v>-3.0000000000000027E-2</v>
       </c>
-      <c r="U46" s="128">
+      <c r="U46" s="127">
         <f>L46-S46</f>
         <v>4.9999999999999822E-2</v>
       </c>
-      <c r="V46" s="145">
+      <c r="V46" s="129">
         <f>U46/590</f>
         <v>8.4745762711864101E-5</v>
       </c>
-      <c r="W46" s="132">
+      <c r="W46" s="93">
         <f>(U46/L46)*100</f>
         <v>0.83892617449664131</v>
       </c>
-      <c r="X46" s="100" t="s">
+      <c r="X46" s="98" t="s">
         <v>132</v>
       </c>
-      <c r="Y46" s="135"/>
+      <c r="Y46" s="122"/>
     </row>
     <row r="47" spans="2:25" x14ac:dyDescent="0.35">
-      <c r="B47" s="119"/>
-      <c r="C47" s="119"/>
-      <c r="D47" s="119"/>
-      <c r="E47" s="119"/>
-      <c r="F47" s="119"/>
-      <c r="G47" s="126"/>
-      <c r="H47" s="119"/>
+      <c r="B47" s="121"/>
+      <c r="C47" s="121"/>
+      <c r="D47" s="121"/>
+      <c r="E47" s="121"/>
+      <c r="F47" s="121"/>
+      <c r="G47" s="125"/>
+      <c r="H47" s="121"/>
       <c r="I47" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="J47" s="126"/>
+      <c r="J47" s="125"/>
       <c r="K47" s="60">
         <v>2.37</v>
       </c>
-      <c r="L47" s="126"/>
+      <c r="L47" s="125"/>
       <c r="M47" s="61"/>
-      <c r="N47" s="119"/>
-      <c r="O47" s="119"/>
-      <c r="P47" s="95"/>
+      <c r="N47" s="121"/>
+      <c r="O47" s="121"/>
+      <c r="P47" s="92"/>
       <c r="Q47" s="38" t="s">
         <v>162</v>
       </c>
       <c r="R47" s="3">
         <v>2.33</v>
       </c>
-      <c r="S47" s="119"/>
+      <c r="S47" s="121"/>
       <c r="T47" s="3">
         <f t="shared" si="3"/>
         <v>4.0000000000000036E-2</v>
       </c>
-      <c r="U47" s="129"/>
-      <c r="V47" s="146"/>
-      <c r="W47" s="133"/>
-      <c r="X47" s="119"/>
-      <c r="Y47" s="136"/>
+      <c r="U47" s="128"/>
+      <c r="V47" s="130"/>
+      <c r="W47" s="120"/>
+      <c r="X47" s="121"/>
+      <c r="Y47" s="123"/>
     </row>
     <row r="48" spans="2:25" x14ac:dyDescent="0.35">
-      <c r="B48" s="101"/>
-      <c r="C48" s="101"/>
-      <c r="D48" s="101"/>
-      <c r="E48" s="101"/>
-      <c r="F48" s="101"/>
-      <c r="G48" s="114"/>
-      <c r="H48" s="101"/>
+      <c r="B48" s="99"/>
+      <c r="C48" s="99"/>
+      <c r="D48" s="99"/>
+      <c r="E48" s="99"/>
+      <c r="F48" s="99"/>
+      <c r="G48" s="101"/>
+      <c r="H48" s="99"/>
       <c r="I48" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="J48" s="114"/>
+      <c r="J48" s="101"/>
       <c r="K48" s="60">
         <v>2.37</v>
       </c>
-      <c r="L48" s="114"/>
+      <c r="L48" s="101"/>
       <c r="M48" s="61"/>
-      <c r="N48" s="101"/>
-      <c r="O48" s="101"/>
-      <c r="P48" s="95"/>
+      <c r="N48" s="99"/>
+      <c r="O48" s="99"/>
+      <c r="P48" s="92"/>
       <c r="Q48" s="38" t="s">
         <v>164</v>
       </c>
       <c r="R48" s="3">
         <v>2.33</v>
       </c>
-      <c r="S48" s="101"/>
+      <c r="S48" s="99"/>
       <c r="T48" s="3">
         <f t="shared" si="3"/>
         <v>4.0000000000000036E-2</v>
       </c>
-      <c r="U48" s="130"/>
-      <c r="V48" s="147"/>
-      <c r="W48" s="134"/>
-      <c r="X48" s="101"/>
-      <c r="Y48" s="137"/>
+      <c r="U48" s="94"/>
+      <c r="V48" s="131"/>
+      <c r="W48" s="97"/>
+      <c r="X48" s="99"/>
+      <c r="Y48" s="124"/>
     </row>
     <row r="49" spans="2:25" x14ac:dyDescent="0.35">
-      <c r="B49" s="95">
+      <c r="B49" s="92">
         <v>20</v>
       </c>
-      <c r="C49" s="95" t="s">
+      <c r="C49" s="92" t="s">
         <v>25</v>
       </c>
-      <c r="D49" s="95" t="s">
+      <c r="D49" s="92" t="s">
         <v>46</v>
       </c>
-      <c r="E49" s="103" t="s">
+      <c r="E49" s="109" t="s">
         <v>130</v>
       </c>
-      <c r="F49" s="100" t="s">
+      <c r="F49" s="98" t="s">
         <v>157</v>
       </c>
-      <c r="G49" s="100" t="s">
+      <c r="G49" s="98" t="s">
         <v>165</v>
       </c>
-      <c r="H49" s="100">
+      <c r="H49" s="98">
         <v>6000004468</v>
       </c>
       <c r="I49" s="38" t="s">
         <v>166</v>
       </c>
-      <c r="J49" s="113" t="s">
+      <c r="J49" s="100" t="s">
         <v>146</v>
       </c>
       <c r="K49" s="56">
         <f>13.58*86.14</f>
         <v>1169.7812000000001</v>
       </c>
-      <c r="L49" s="113">
+      <c r="L49" s="100">
         <f>K49+K50+K51</f>
         <v>3319.8355999999999</v>
       </c>
       <c r="M49" s="61"/>
-      <c r="N49" s="113" t="s">
+      <c r="N49" s="100" t="s">
         <v>95</v>
       </c>
-      <c r="O49" s="113" t="s">
+      <c r="O49" s="100" t="s">
         <v>130</v>
       </c>
-      <c r="P49" s="96" t="s">
+      <c r="P49" s="103" t="s">
         <v>201</v>
       </c>
       <c r="Q49" s="38" t="s">
@@ -6957,7 +6957,7 @@
       <c r="R49" s="38">
         <v>1263</v>
       </c>
-      <c r="S49" s="96">
+      <c r="S49" s="103">
         <f>R49+R50+R51</f>
         <v>3608</v>
       </c>
@@ -6965,120 +6965,120 @@
         <f t="shared" si="3"/>
         <v>-93.218799999999874</v>
       </c>
-      <c r="U49" s="132">
+      <c r="U49" s="93">
         <f>L49-S49</f>
         <v>-288.16440000000011</v>
       </c>
-      <c r="V49" s="132">
+      <c r="V49" s="93">
         <f>U49/590</f>
         <v>-0.48841423728813577</v>
       </c>
-      <c r="W49" s="132">
+      <c r="W49" s="93">
         <f>(U49/L49)*100</f>
         <v>-8.6800804232595183</v>
       </c>
-      <c r="X49" s="100" t="s">
+      <c r="X49" s="98" t="s">
         <v>149</v>
       </c>
-      <c r="Y49" s="135"/>
+      <c r="Y49" s="122"/>
     </row>
     <row r="50" spans="2:25" x14ac:dyDescent="0.35">
-      <c r="B50" s="95"/>
-      <c r="C50" s="95"/>
-      <c r="D50" s="95"/>
-      <c r="E50" s="103"/>
-      <c r="F50" s="119"/>
-      <c r="G50" s="119"/>
-      <c r="H50" s="119"/>
+      <c r="B50" s="92"/>
+      <c r="C50" s="92"/>
+      <c r="D50" s="92"/>
+      <c r="E50" s="109"/>
+      <c r="F50" s="121"/>
+      <c r="G50" s="121"/>
+      <c r="H50" s="121"/>
       <c r="I50" s="38" t="s">
         <v>170</v>
       </c>
-      <c r="J50" s="126"/>
+      <c r="J50" s="125"/>
       <c r="K50" s="56">
         <f>12.48*86.14</f>
         <v>1075.0272</v>
       </c>
-      <c r="L50" s="126"/>
+      <c r="L50" s="125"/>
       <c r="M50" s="61"/>
-      <c r="N50" s="126"/>
-      <c r="O50" s="126"/>
-      <c r="P50" s="127"/>
+      <c r="N50" s="125"/>
+      <c r="O50" s="125"/>
+      <c r="P50" s="126"/>
       <c r="Q50" s="38" t="s">
         <v>203</v>
       </c>
       <c r="R50" s="38">
         <v>1166</v>
       </c>
-      <c r="S50" s="127"/>
+      <c r="S50" s="126"/>
       <c r="T50" s="57">
         <f t="shared" si="3"/>
         <v>-90.972800000000007</v>
       </c>
-      <c r="U50" s="133"/>
-      <c r="V50" s="133"/>
-      <c r="W50" s="133"/>
-      <c r="X50" s="119"/>
-      <c r="Y50" s="136"/>
+      <c r="U50" s="120"/>
+      <c r="V50" s="120"/>
+      <c r="W50" s="120"/>
+      <c r="X50" s="121"/>
+      <c r="Y50" s="123"/>
     </row>
     <row r="51" spans="2:25" x14ac:dyDescent="0.35">
-      <c r="B51" s="95"/>
-      <c r="C51" s="95"/>
-      <c r="D51" s="95"/>
-      <c r="E51" s="103"/>
-      <c r="F51" s="101"/>
-      <c r="G51" s="101"/>
-      <c r="H51" s="101"/>
+      <c r="B51" s="92"/>
+      <c r="C51" s="92"/>
+      <c r="D51" s="92"/>
+      <c r="E51" s="109"/>
+      <c r="F51" s="99"/>
+      <c r="G51" s="99"/>
+      <c r="H51" s="99"/>
       <c r="I51" s="38" t="s">
         <v>172</v>
       </c>
-      <c r="J51" s="114"/>
+      <c r="J51" s="101"/>
       <c r="K51" s="56">
         <f>12.48*86.14</f>
         <v>1075.0272</v>
       </c>
-      <c r="L51" s="114"/>
+      <c r="L51" s="101"/>
       <c r="M51" s="61"/>
-      <c r="N51" s="114"/>
-      <c r="O51" s="114"/>
-      <c r="P51" s="97"/>
+      <c r="N51" s="101"/>
+      <c r="O51" s="101"/>
+      <c r="P51" s="104"/>
       <c r="Q51" s="38" t="s">
         <v>204</v>
       </c>
       <c r="R51" s="3">
         <v>1179</v>
       </c>
-      <c r="S51" s="97"/>
+      <c r="S51" s="104"/>
       <c r="T51" s="57">
         <f t="shared" si="3"/>
         <v>-103.97280000000001</v>
       </c>
-      <c r="U51" s="134"/>
-      <c r="V51" s="134"/>
-      <c r="W51" s="134"/>
-      <c r="X51" s="101"/>
-      <c r="Y51" s="137"/>
+      <c r="U51" s="97"/>
+      <c r="V51" s="97"/>
+      <c r="W51" s="97"/>
+      <c r="X51" s="99"/>
+      <c r="Y51" s="124"/>
     </row>
     <row r="60" spans="2:25" x14ac:dyDescent="0.35">
       <c r="C60" s="1"/>
       <c r="D60" s="1"/>
       <c r="E60" s="1"/>
-      <c r="G60" s="92" t="s">
+      <c r="G60" s="117" t="s">
         <v>97</v>
       </c>
-      <c r="H60" s="93"/>
-      <c r="I60" s="93"/>
-      <c r="J60" s="93"/>
-      <c r="K60" s="93"/>
-      <c r="L60" s="94"/>
+      <c r="H60" s="118"/>
+      <c r="I60" s="118"/>
+      <c r="J60" s="118"/>
+      <c r="K60" s="118"/>
+      <c r="L60" s="119"/>
       <c r="M60" s="24"/>
-      <c r="N60" s="92" t="s">
+      <c r="N60" s="117" t="s">
         <v>98</v>
       </c>
-      <c r="O60" s="93"/>
-      <c r="P60" s="93"/>
-      <c r="Q60" s="93"/>
-      <c r="R60" s="93"/>
-      <c r="S60" s="94"/>
+      <c r="O60" s="118"/>
+      <c r="P60" s="118"/>
+      <c r="Q60" s="118"/>
+      <c r="R60" s="118"/>
+      <c r="S60" s="119"/>
       <c r="T60" s="25"/>
       <c r="W60" s="26"/>
       <c r="X60" s="1"/>
@@ -7152,46 +7152,46 @@
       </c>
     </row>
     <row r="62" spans="2:25" x14ac:dyDescent="0.35">
-      <c r="C62" s="95" t="s">
+      <c r="C62" s="92" t="s">
         <v>13</v>
       </c>
-      <c r="D62" s="96" t="s">
+      <c r="D62" s="103" t="s">
         <v>142</v>
       </c>
-      <c r="E62" s="100" t="s">
+      <c r="E62" s="98" t="s">
         <v>130</v>
       </c>
-      <c r="F62" s="100" t="s">
+      <c r="F62" s="98" t="s">
         <v>143</v>
       </c>
-      <c r="G62" s="100" t="s">
+      <c r="G62" s="98" t="s">
         <v>144</v>
       </c>
-      <c r="H62" s="100">
+      <c r="H62" s="98">
         <v>6000004401</v>
       </c>
       <c r="I62" s="38" t="s">
         <v>145</v>
       </c>
-      <c r="J62" s="103" t="s">
+      <c r="J62" s="109" t="s">
         <v>146</v>
       </c>
       <c r="K62" s="56">
         <f>0.9*86.14</f>
         <v>77.525999999999996</v>
       </c>
-      <c r="L62" s="113">
+      <c r="L62" s="100">
         <f>K62+K63</f>
         <v>142.9924</v>
       </c>
-      <c r="M62" s="115"/>
-      <c r="N62" s="95" t="s">
+      <c r="M62" s="111"/>
+      <c r="N62" s="92" t="s">
         <v>95</v>
       </c>
-      <c r="O62" s="95" t="s">
+      <c r="O62" s="92" t="s">
         <v>135</v>
       </c>
-      <c r="P62" s="96" t="s">
+      <c r="P62" s="103" t="s">
         <v>147</v>
       </c>
       <c r="Q62" s="3" t="s">
@@ -7200,7 +7200,7 @@
       <c r="R62" s="38">
         <v>86</v>
       </c>
-      <c r="S62" s="96">
+      <c r="S62" s="103">
         <f>R62+R63</f>
         <v>165</v>
       </c>
@@ -7208,97 +7208,97 @@
         <f>K62-R62</f>
         <v>-8.4740000000000038</v>
       </c>
-      <c r="U62" s="106">
+      <c r="U62" s="113">
         <f>L62-S62</f>
         <v>-22.007599999999996</v>
       </c>
-      <c r="V62" s="117">
+      <c r="V62" s="95">
         <f>U62/590</f>
         <v>-3.7301016949152534E-2</v>
       </c>
-      <c r="W62" s="106">
+      <c r="W62" s="113">
         <f>(U62/L62)*100</f>
         <v>-15.390748039755955</v>
       </c>
-      <c r="X62" s="95" t="s">
+      <c r="X62" s="92" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="63" spans="2:25" x14ac:dyDescent="0.35">
-      <c r="C63" s="95"/>
-      <c r="D63" s="97"/>
-      <c r="E63" s="101"/>
-      <c r="F63" s="101"/>
-      <c r="G63" s="101"/>
-      <c r="H63" s="101"/>
+      <c r="C63" s="92"/>
+      <c r="D63" s="104"/>
+      <c r="E63" s="99"/>
+      <c r="F63" s="99"/>
+      <c r="G63" s="99"/>
+      <c r="H63" s="99"/>
       <c r="I63" s="38" t="s">
         <v>150</v>
       </c>
-      <c r="J63" s="103"/>
+      <c r="J63" s="109"/>
       <c r="K63" s="56">
         <f>0.76*86.14</f>
         <v>65.466400000000007</v>
       </c>
-      <c r="L63" s="114"/>
-      <c r="M63" s="116"/>
-      <c r="N63" s="95"/>
-      <c r="O63" s="95"/>
-      <c r="P63" s="97"/>
+      <c r="L63" s="101"/>
+      <c r="M63" s="112"/>
+      <c r="N63" s="92"/>
+      <c r="O63" s="92"/>
+      <c r="P63" s="104"/>
       <c r="Q63" s="49" t="s">
         <v>151</v>
       </c>
       <c r="R63" s="38">
         <v>79</v>
       </c>
-      <c r="S63" s="97"/>
+      <c r="S63" s="104"/>
       <c r="T63" s="39">
         <f t="shared" ref="T63:T74" si="4">K63-R63</f>
         <v>-13.533599999999993</v>
       </c>
-      <c r="U63" s="106"/>
-      <c r="V63" s="118"/>
-      <c r="W63" s="106"/>
-      <c r="X63" s="95"/>
+      <c r="U63" s="113"/>
+      <c r="V63" s="96"/>
+      <c r="W63" s="113"/>
+      <c r="X63" s="92"/>
     </row>
     <row r="64" spans="2:25" x14ac:dyDescent="0.35">
-      <c r="C64" s="95" t="s">
+      <c r="C64" s="92" t="s">
         <v>25</v>
       </c>
-      <c r="D64" s="96" t="s">
+      <c r="D64" s="103" t="s">
         <v>142</v>
       </c>
-      <c r="E64" s="109" t="s">
+      <c r="E64" s="114" t="s">
         <v>130</v>
       </c>
-      <c r="F64" s="100" t="s">
+      <c r="F64" s="98" t="s">
         <v>143</v>
       </c>
-      <c r="G64" s="102" t="s">
+      <c r="G64" s="115" t="s">
         <v>152</v>
       </c>
-      <c r="H64" s="95">
+      <c r="H64" s="92">
         <v>6000004174</v>
       </c>
       <c r="I64" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="J64" s="103" t="s">
+      <c r="J64" s="109" t="s">
         <v>124</v>
       </c>
       <c r="K64" s="56">
         <v>207.5</v>
       </c>
-      <c r="L64" s="125">
+      <c r="L64" s="110">
         <v>382.5</v>
       </c>
-      <c r="M64" s="115"/>
-      <c r="N64" s="95" t="s">
+      <c r="M64" s="111"/>
+      <c r="N64" s="92" t="s">
         <v>25</v>
       </c>
-      <c r="O64" s="95" t="s">
+      <c r="O64" s="92" t="s">
         <v>130</v>
       </c>
-      <c r="P64" s="96" t="s">
+      <c r="P64" s="103" t="s">
         <v>154</v>
       </c>
       <c r="Q64" s="3" t="s">
@@ -7307,105 +7307,105 @@
       <c r="R64" s="38">
         <v>200</v>
       </c>
-      <c r="S64" s="96">
+      <c r="S64" s="103">
         <v>370</v>
       </c>
       <c r="T64" s="38">
         <f t="shared" si="4"/>
         <v>7.5</v>
       </c>
-      <c r="U64" s="104">
+      <c r="U64" s="116">
         <f>L64-S64</f>
         <v>12.5</v>
       </c>
-      <c r="V64" s="117">
+      <c r="V64" s="95">
         <f>U64/590</f>
         <v>2.1186440677966101E-2</v>
       </c>
-      <c r="W64" s="106">
+      <c r="W64" s="113">
         <f>(U64/L64)*100</f>
         <v>3.2679738562091507</v>
       </c>
-      <c r="X64" s="95" t="s">
+      <c r="X64" s="92" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="65" spans="3:24" x14ac:dyDescent="0.35">
-      <c r="C65" s="95"/>
-      <c r="D65" s="97"/>
-      <c r="E65" s="109"/>
-      <c r="F65" s="101"/>
-      <c r="G65" s="102"/>
-      <c r="H65" s="95"/>
+      <c r="C65" s="92"/>
+      <c r="D65" s="104"/>
+      <c r="E65" s="114"/>
+      <c r="F65" s="99"/>
+      <c r="G65" s="115"/>
+      <c r="H65" s="92"/>
       <c r="I65" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="J65" s="103"/>
+      <c r="J65" s="109"/>
       <c r="K65" s="56">
         <v>175</v>
       </c>
-      <c r="L65" s="125"/>
-      <c r="M65" s="116"/>
-      <c r="N65" s="95"/>
-      <c r="O65" s="95"/>
-      <c r="P65" s="97"/>
+      <c r="L65" s="110"/>
+      <c r="M65" s="112"/>
+      <c r="N65" s="92"/>
+      <c r="O65" s="92"/>
+      <c r="P65" s="104"/>
       <c r="Q65" s="49" t="s">
         <v>151</v>
       </c>
       <c r="R65" s="38">
         <v>170</v>
       </c>
-      <c r="S65" s="97"/>
+      <c r="S65" s="104"/>
       <c r="T65" s="38">
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="U65" s="104"/>
-      <c r="V65" s="118"/>
-      <c r="W65" s="106"/>
-      <c r="X65" s="95"/>
+      <c r="U65" s="116"/>
+      <c r="V65" s="96"/>
+      <c r="W65" s="113"/>
+      <c r="X65" s="92"/>
     </row>
     <row r="66" spans="3:24" x14ac:dyDescent="0.35">
-      <c r="C66" s="100" t="s">
+      <c r="C66" s="98" t="s">
         <v>13</v>
       </c>
-      <c r="D66" s="96" t="s">
+      <c r="D66" s="103" t="s">
         <v>142</v>
       </c>
-      <c r="E66" s="100" t="s">
+      <c r="E66" s="98" t="s">
         <v>130</v>
       </c>
-      <c r="F66" s="100" t="s">
+      <c r="F66" s="98" t="s">
         <v>143</v>
       </c>
-      <c r="G66" s="100" t="s">
+      <c r="G66" s="98" t="s">
         <v>144</v>
       </c>
-      <c r="H66" s="100">
+      <c r="H66" s="98">
         <v>6000004401</v>
       </c>
       <c r="I66" s="38" t="s">
         <v>145</v>
       </c>
-      <c r="J66" s="103" t="s">
+      <c r="J66" s="109" t="s">
         <v>146</v>
       </c>
       <c r="K66" s="56">
         <f>0.9*86.14</f>
         <v>77.525999999999996</v>
       </c>
-      <c r="L66" s="113">
+      <c r="L66" s="100">
         <f>K66+K67</f>
         <v>142.9924</v>
       </c>
       <c r="M66" s="61"/>
-      <c r="N66" s="95" t="s">
+      <c r="N66" s="92" t="s">
         <v>95</v>
       </c>
-      <c r="O66" s="95" t="s">
+      <c r="O66" s="92" t="s">
         <v>135</v>
       </c>
-      <c r="P66" s="103" t="s">
+      <c r="P66" s="109" t="s">
         <v>179</v>
       </c>
       <c r="Q66" s="38" t="s">
@@ -7414,7 +7414,7 @@
       <c r="R66" s="3">
         <v>100</v>
       </c>
-      <c r="S66" s="95">
+      <c r="S66" s="92">
         <f>R66+R67</f>
         <v>179</v>
       </c>
@@ -7422,99 +7422,99 @@
         <f t="shared" si="4"/>
         <v>-22.474000000000004</v>
       </c>
-      <c r="U66" s="132">
+      <c r="U66" s="93">
         <f>L66-S66</f>
         <v>-36.007599999999996</v>
       </c>
-      <c r="V66" s="117">
+      <c r="V66" s="95">
         <f>U66/590</f>
         <v>-6.1029830508474568E-2</v>
       </c>
-      <c r="W66" s="132">
+      <c r="W66" s="93">
         <f>(U66/L66)*100</f>
         <v>-25.181478176462523</v>
       </c>
-      <c r="X66" s="100" t="s">
+      <c r="X66" s="98" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="67" spans="3:24" x14ac:dyDescent="0.35">
-      <c r="C67" s="101"/>
-      <c r="D67" s="97"/>
-      <c r="E67" s="101"/>
-      <c r="F67" s="101"/>
-      <c r="G67" s="101"/>
-      <c r="H67" s="101"/>
+      <c r="C67" s="99"/>
+      <c r="D67" s="104"/>
+      <c r="E67" s="99"/>
+      <c r="F67" s="99"/>
+      <c r="G67" s="99"/>
+      <c r="H67" s="99"/>
       <c r="I67" s="38" t="s">
         <v>150</v>
       </c>
-      <c r="J67" s="103"/>
+      <c r="J67" s="109"/>
       <c r="K67" s="56">
         <f>0.76*86.14</f>
         <v>65.466400000000007</v>
       </c>
-      <c r="L67" s="114"/>
+      <c r="L67" s="101"/>
       <c r="M67" s="61"/>
-      <c r="N67" s="95"/>
-      <c r="O67" s="95"/>
-      <c r="P67" s="103"/>
+      <c r="N67" s="92"/>
+      <c r="O67" s="92"/>
+      <c r="P67" s="109"/>
       <c r="Q67" s="38" t="s">
         <v>150</v>
       </c>
       <c r="R67" s="3">
         <v>79</v>
       </c>
-      <c r="S67" s="95"/>
+      <c r="S67" s="92"/>
       <c r="T67" s="62">
         <f t="shared" si="4"/>
         <v>-13.533599999999993</v>
       </c>
-      <c r="U67" s="134"/>
-      <c r="V67" s="118"/>
-      <c r="W67" s="134"/>
-      <c r="X67" s="101"/>
+      <c r="U67" s="97"/>
+      <c r="V67" s="96"/>
+      <c r="W67" s="97"/>
+      <c r="X67" s="99"/>
     </row>
     <row r="68" spans="3:24" x14ac:dyDescent="0.35">
-      <c r="C68" s="100" t="s">
+      <c r="C68" s="98" t="s">
         <v>13</v>
       </c>
-      <c r="D68" s="96" t="s">
+      <c r="D68" s="103" t="s">
         <v>142</v>
       </c>
-      <c r="E68" s="100" t="s">
+      <c r="E68" s="98" t="s">
         <v>130</v>
       </c>
-      <c r="F68" s="100" t="s">
+      <c r="F68" s="98" t="s">
         <v>143</v>
       </c>
-      <c r="G68" s="100" t="s">
+      <c r="G68" s="98" t="s">
         <v>144</v>
       </c>
-      <c r="H68" s="100">
+      <c r="H68" s="98">
         <v>6000004401</v>
       </c>
       <c r="I68" s="38" t="s">
         <v>180</v>
       </c>
-      <c r="J68" s="103" t="s">
+      <c r="J68" s="109" t="s">
         <v>146</v>
       </c>
       <c r="K68" s="56">
         <f>0.9*86.14</f>
         <v>77.525999999999996</v>
       </c>
-      <c r="L68" s="113">
+      <c r="L68" s="100">
         <f>K68+K69</f>
         <v>142.9924</v>
       </c>
       <c r="M68" s="61"/>
-      <c r="N68" s="95" t="s">
+      <c r="N68" s="92" t="s">
         <v>95</v>
       </c>
-      <c r="O68" s="95" t="s">
+      <c r="O68" s="92" t="s">
         <v>135</v>
       </c>
-      <c r="P68" s="103" t="s">
+      <c r="P68" s="109" t="s">
         <v>181</v>
       </c>
       <c r="Q68" s="38" t="s">
@@ -7523,7 +7523,7 @@
       <c r="R68" s="3">
         <v>96</v>
       </c>
-      <c r="S68" s="95">
+      <c r="S68" s="92">
         <f>R68+R69</f>
         <v>181</v>
       </c>
@@ -7531,101 +7531,101 @@
         <f t="shared" si="4"/>
         <v>-18.474000000000004</v>
       </c>
-      <c r="U68" s="132">
+      <c r="U68" s="93">
         <f>L68-S68</f>
         <v>-38.007599999999996</v>
       </c>
-      <c r="V68" s="117">
+      <c r="V68" s="95">
         <f>U68/590</f>
         <v>-6.4419661016949153E-2</v>
       </c>
-      <c r="W68" s="132">
+      <c r="W68" s="93">
         <f>(U68/L68)*100</f>
         <v>-26.580153910277748</v>
       </c>
-      <c r="X68" s="100" t="s">
+      <c r="X68" s="98" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="69" spans="3:24" x14ac:dyDescent="0.35">
-      <c r="C69" s="101"/>
-      <c r="D69" s="97"/>
-      <c r="E69" s="101"/>
-      <c r="F69" s="101"/>
-      <c r="G69" s="101"/>
-      <c r="H69" s="101"/>
+      <c r="C69" s="99"/>
+      <c r="D69" s="104"/>
+      <c r="E69" s="99"/>
+      <c r="F69" s="99"/>
+      <c r="G69" s="99"/>
+      <c r="H69" s="99"/>
       <c r="I69" s="38" t="s">
         <v>182</v>
       </c>
-      <c r="J69" s="103"/>
+      <c r="J69" s="109"/>
       <c r="K69" s="56">
         <f>0.76*86.14</f>
         <v>65.466400000000007</v>
       </c>
-      <c r="L69" s="114"/>
+      <c r="L69" s="101"/>
       <c r="M69" s="61"/>
-      <c r="N69" s="95"/>
-      <c r="O69" s="95"/>
-      <c r="P69" s="103"/>
+      <c r="N69" s="92"/>
+      <c r="O69" s="92"/>
+      <c r="P69" s="109"/>
       <c r="Q69" s="38" t="s">
         <v>150</v>
       </c>
       <c r="R69" s="3">
         <v>85</v>
       </c>
-      <c r="S69" s="95"/>
+      <c r="S69" s="92"/>
       <c r="T69" s="46">
         <f t="shared" si="4"/>
         <v>-19.533599999999993</v>
       </c>
-      <c r="U69" s="134"/>
-      <c r="V69" s="118"/>
-      <c r="W69" s="134"/>
-      <c r="X69" s="101"/>
+      <c r="U69" s="97"/>
+      <c r="V69" s="96"/>
+      <c r="W69" s="97"/>
+      <c r="X69" s="99"/>
     </row>
     <row r="70" spans="3:24" x14ac:dyDescent="0.35">
-      <c r="C70" s="100" t="s">
+      <c r="C70" s="98" t="s">
         <v>186</v>
       </c>
-      <c r="D70" s="96" t="s">
+      <c r="D70" s="103" t="s">
         <v>142</v>
       </c>
-      <c r="E70" s="100" t="s">
+      <c r="E70" s="98" t="s">
         <v>130</v>
       </c>
-      <c r="F70" s="100" t="s">
+      <c r="F70" s="98" t="s">
         <v>143</v>
       </c>
-      <c r="G70" s="100" t="s">
+      <c r="G70" s="98" t="s">
         <v>187</v>
       </c>
-      <c r="H70" s="100">
+      <c r="H70" s="98">
         <v>6000004383</v>
       </c>
       <c r="I70" s="38" t="s">
         <v>145</v>
       </c>
-      <c r="J70" s="103" t="s">
+      <c r="J70" s="109" t="s">
         <v>146</v>
       </c>
       <c r="K70" s="56">
         <f>0.9*86.14</f>
         <v>77.525999999999996</v>
       </c>
-      <c r="L70" s="138">
+      <c r="L70" s="102">
         <f>K70+K71</f>
         <v>142.9924</v>
       </c>
-      <c r="M70" s="142">
+      <c r="M70" s="105">
         <v>45853</v>
       </c>
-      <c r="N70" s="95" t="s">
+      <c r="N70" s="92" t="s">
         <v>95</v>
       </c>
-      <c r="O70" s="107" t="s">
+      <c r="O70" s="106" t="s">
         <v>130</v>
       </c>
-      <c r="P70" s="103" t="s">
+      <c r="P70" s="109" t="s">
         <v>188</v>
       </c>
       <c r="Q70" s="38" t="s">
@@ -7634,7 +7634,7 @@
       <c r="R70" s="3">
         <v>90</v>
       </c>
-      <c r="S70" s="95">
+      <c r="S70" s="92">
         <f>R70+R71</f>
         <v>165</v>
       </c>
@@ -7642,101 +7642,101 @@
         <f t="shared" si="4"/>
         <v>-12.474000000000004</v>
       </c>
-      <c r="U70" s="132">
+      <c r="U70" s="93">
         <f>L70-S70</f>
         <v>-22.007599999999996</v>
       </c>
-      <c r="V70" s="132">
+      <c r="V70" s="93">
         <f>U70/590</f>
         <v>-3.7301016949152534E-2</v>
       </c>
-      <c r="W70" s="132">
+      <c r="W70" s="93">
         <f>(U70/L70)*100</f>
         <v>-15.390748039755955</v>
       </c>
-      <c r="X70" s="100" t="s">
+      <c r="X70" s="98" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="71" spans="3:24" x14ac:dyDescent="0.35">
-      <c r="C71" s="101"/>
-      <c r="D71" s="97"/>
-      <c r="E71" s="101"/>
-      <c r="F71" s="101"/>
-      <c r="G71" s="101"/>
-      <c r="H71" s="101"/>
+      <c r="C71" s="99"/>
+      <c r="D71" s="104"/>
+      <c r="E71" s="99"/>
+      <c r="F71" s="99"/>
+      <c r="G71" s="99"/>
+      <c r="H71" s="99"/>
       <c r="I71" s="38" t="s">
         <v>150</v>
       </c>
-      <c r="J71" s="103"/>
+      <c r="J71" s="109"/>
       <c r="K71" s="56">
         <f>0.76*86.14</f>
         <v>65.466400000000007</v>
       </c>
-      <c r="L71" s="114"/>
-      <c r="M71" s="142"/>
-      <c r="N71" s="95"/>
-      <c r="O71" s="107"/>
-      <c r="P71" s="103"/>
+      <c r="L71" s="101"/>
+      <c r="M71" s="105"/>
+      <c r="N71" s="92"/>
+      <c r="O71" s="106"/>
+      <c r="P71" s="109"/>
       <c r="Q71" s="38" t="s">
         <v>150</v>
       </c>
       <c r="R71" s="3">
         <v>75</v>
       </c>
-      <c r="S71" s="95"/>
+      <c r="S71" s="92"/>
       <c r="T71" s="46">
         <f t="shared" si="4"/>
         <v>-9.5335999999999927</v>
       </c>
-      <c r="U71" s="130"/>
-      <c r="V71" s="134"/>
-      <c r="W71" s="134"/>
-      <c r="X71" s="101"/>
+      <c r="U71" s="94"/>
+      <c r="V71" s="97"/>
+      <c r="W71" s="97"/>
+      <c r="X71" s="99"/>
     </row>
     <row r="72" spans="3:24" x14ac:dyDescent="0.35">
-      <c r="C72" s="100" t="s">
+      <c r="C72" s="98" t="s">
         <v>186</v>
       </c>
-      <c r="D72" s="96" t="s">
+      <c r="D72" s="103" t="s">
         <v>142</v>
       </c>
-      <c r="E72" s="100" t="s">
+      <c r="E72" s="98" t="s">
         <v>130</v>
       </c>
-      <c r="F72" s="100" t="s">
+      <c r="F72" s="98" t="s">
         <v>143</v>
       </c>
-      <c r="G72" s="100" t="s">
+      <c r="G72" s="98" t="s">
         <v>187</v>
       </c>
-      <c r="H72" s="100">
+      <c r="H72" s="98">
         <v>6000004382</v>
       </c>
       <c r="I72" s="38" t="s">
         <v>196</v>
       </c>
-      <c r="J72" s="103" t="s">
+      <c r="J72" s="109" t="s">
         <v>146</v>
       </c>
       <c r="K72" s="56">
         <f>0.9*86.14</f>
         <v>77.525999999999996</v>
       </c>
-      <c r="L72" s="138">
+      <c r="L72" s="102">
         <f>K72+K73</f>
         <v>142.9924</v>
       </c>
-      <c r="M72" s="142">
+      <c r="M72" s="105">
         <v>45853</v>
       </c>
-      <c r="N72" s="95" t="s">
+      <c r="N72" s="92" t="s">
         <v>95</v>
       </c>
-      <c r="O72" s="107" t="s">
+      <c r="O72" s="106" t="s">
         <v>130</v>
       </c>
-      <c r="P72" s="95" t="s">
+      <c r="P72" s="92" t="s">
         <v>197</v>
       </c>
       <c r="Q72" s="38" t="s">
@@ -7745,7 +7745,7 @@
       <c r="R72" s="3">
         <v>90</v>
       </c>
-      <c r="S72" s="95">
+      <c r="S72" s="92">
         <f>R72+R73</f>
         <v>175</v>
       </c>
@@ -7753,101 +7753,101 @@
         <f t="shared" si="4"/>
         <v>-12.474000000000004</v>
       </c>
-      <c r="U72" s="132">
+      <c r="U72" s="93">
         <f>L72-S72</f>
         <v>-32.007599999999996</v>
       </c>
-      <c r="V72" s="132">
+      <c r="V72" s="93">
         <f>U72/590</f>
         <v>-5.4250169491525418E-2</v>
       </c>
-      <c r="W72" s="117">
+      <c r="W72" s="95">
         <f>(U72/L72)*100</f>
         <v>-22.384126708832074</v>
       </c>
-      <c r="X72" s="100" t="s">
+      <c r="X72" s="98" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="73" spans="3:24" x14ac:dyDescent="0.35">
-      <c r="C73" s="101"/>
-      <c r="D73" s="97"/>
-      <c r="E73" s="101"/>
-      <c r="F73" s="101"/>
-      <c r="G73" s="101"/>
-      <c r="H73" s="101"/>
+      <c r="C73" s="99"/>
+      <c r="D73" s="104"/>
+      <c r="E73" s="99"/>
+      <c r="F73" s="99"/>
+      <c r="G73" s="99"/>
+      <c r="H73" s="99"/>
       <c r="I73" s="38" t="s">
         <v>198</v>
       </c>
-      <c r="J73" s="103"/>
+      <c r="J73" s="109"/>
       <c r="K73" s="56">
         <f>0.76*86.14</f>
         <v>65.466400000000007</v>
       </c>
-      <c r="L73" s="114"/>
-      <c r="M73" s="142"/>
-      <c r="N73" s="95"/>
-      <c r="O73" s="107"/>
-      <c r="P73" s="95"/>
+      <c r="L73" s="101"/>
+      <c r="M73" s="105"/>
+      <c r="N73" s="92"/>
+      <c r="O73" s="106"/>
+      <c r="P73" s="92"/>
       <c r="Q73" s="38" t="s">
         <v>150</v>
       </c>
       <c r="R73" s="3">
         <v>85</v>
       </c>
-      <c r="S73" s="95"/>
+      <c r="S73" s="92"/>
       <c r="T73" s="46">
         <f t="shared" si="4"/>
         <v>-19.533599999999993</v>
       </c>
-      <c r="U73" s="130"/>
-      <c r="V73" s="134"/>
-      <c r="W73" s="118"/>
-      <c r="X73" s="101"/>
+      <c r="U73" s="94"/>
+      <c r="V73" s="97"/>
+      <c r="W73" s="96"/>
+      <c r="X73" s="99"/>
     </row>
     <row r="74" spans="3:24" x14ac:dyDescent="0.35">
-      <c r="C74" s="100" t="s">
+      <c r="C74" s="98" t="s">
         <v>186</v>
       </c>
-      <c r="D74" s="96" t="s">
+      <c r="D74" s="103" t="s">
         <v>142</v>
       </c>
-      <c r="E74" s="100" t="s">
+      <c r="E74" s="98" t="s">
         <v>130</v>
       </c>
-      <c r="F74" s="100" t="s">
+      <c r="F74" s="98" t="s">
         <v>143</v>
       </c>
-      <c r="G74" s="100" t="s">
+      <c r="G74" s="98" t="s">
         <v>187</v>
       </c>
-      <c r="H74" s="100">
+      <c r="H74" s="98">
         <v>6000004383</v>
       </c>
       <c r="I74" s="38" t="s">
         <v>145</v>
       </c>
-      <c r="J74" s="113" t="s">
+      <c r="J74" s="100" t="s">
         <v>131</v>
       </c>
       <c r="K74" s="56">
         <f>0.9</f>
         <v>0.9</v>
       </c>
-      <c r="L74" s="138">
+      <c r="L74" s="102">
         <f>K74+K75</f>
         <v>1.6600000000000001</v>
       </c>
-      <c r="M74" s="142">
+      <c r="M74" s="105">
         <v>45853</v>
       </c>
-      <c r="N74" s="95" t="s">
+      <c r="N74" s="92" t="s">
         <v>25</v>
       </c>
-      <c r="O74" s="107" t="s">
+      <c r="O74" s="106" t="s">
         <v>130</v>
       </c>
-      <c r="P74" s="95" t="s">
+      <c r="P74" s="92" t="s">
         <v>199</v>
       </c>
       <c r="Q74" s="38" t="s">
@@ -7856,7 +7856,7 @@
       <c r="R74" s="3">
         <v>0.76</v>
       </c>
-      <c r="S74" s="95">
+      <c r="S74" s="92">
         <f>R74+R75</f>
         <v>1.4100000000000001</v>
       </c>
@@ -7864,99 +7864,99 @@
         <f t="shared" si="4"/>
         <v>0.14000000000000001</v>
       </c>
-      <c r="U74" s="132">
+      <c r="U74" s="93">
         <f>L74-S74</f>
         <v>0.25</v>
       </c>
-      <c r="V74" s="139">
+      <c r="V74" s="107">
         <f>U74/590</f>
         <v>4.2372881355932202E-4</v>
       </c>
-      <c r="W74" s="117">
+      <c r="W74" s="95">
         <f>(V74/L74)*100</f>
         <v>2.5525832142127829E-2</v>
       </c>
-      <c r="X74" s="100" t="s">
+      <c r="X74" s="98" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="75" spans="3:24" x14ac:dyDescent="0.35">
-      <c r="C75" s="101"/>
-      <c r="D75" s="97"/>
-      <c r="E75" s="101"/>
-      <c r="F75" s="101"/>
-      <c r="G75" s="101"/>
-      <c r="H75" s="101"/>
+      <c r="C75" s="99"/>
+      <c r="D75" s="104"/>
+      <c r="E75" s="99"/>
+      <c r="F75" s="99"/>
+      <c r="G75" s="99"/>
+      <c r="H75" s="99"/>
       <c r="I75" s="38" t="s">
         <v>150</v>
       </c>
-      <c r="J75" s="114"/>
+      <c r="J75" s="101"/>
       <c r="K75" s="56">
         <f>0.76</f>
         <v>0.76</v>
       </c>
-      <c r="L75" s="114"/>
-      <c r="M75" s="142"/>
-      <c r="N75" s="95"/>
-      <c r="O75" s="107"/>
-      <c r="P75" s="95"/>
+      <c r="L75" s="101"/>
+      <c r="M75" s="105"/>
+      <c r="N75" s="92"/>
+      <c r="O75" s="106"/>
+      <c r="P75" s="92"/>
       <c r="Q75" s="38" t="s">
         <v>150</v>
       </c>
       <c r="R75" s="3">
         <v>0.65</v>
       </c>
-      <c r="S75" s="95"/>
+      <c r="S75" s="92"/>
       <c r="T75" s="57">
         <f>K74-R75</f>
         <v>0.25</v>
       </c>
-      <c r="U75" s="130"/>
-      <c r="V75" s="141"/>
-      <c r="W75" s="118"/>
-      <c r="X75" s="101"/>
+      <c r="U75" s="94"/>
+      <c r="V75" s="108"/>
+      <c r="W75" s="96"/>
+      <c r="X75" s="99"/>
     </row>
     <row r="76" spans="3:24" x14ac:dyDescent="0.35">
-      <c r="C76" s="100" t="s">
+      <c r="C76" s="98" t="s">
         <v>186</v>
       </c>
-      <c r="D76" s="96" t="s">
+      <c r="D76" s="103" t="s">
         <v>142</v>
       </c>
-      <c r="E76" s="100" t="s">
+      <c r="E76" s="98" t="s">
         <v>130</v>
       </c>
-      <c r="F76" s="100" t="s">
+      <c r="F76" s="98" t="s">
         <v>143</v>
       </c>
-      <c r="G76" s="100" t="s">
+      <c r="G76" s="98" t="s">
         <v>187</v>
       </c>
-      <c r="H76" s="100">
+      <c r="H76" s="98">
         <v>6000004384</v>
       </c>
       <c r="I76" s="38" t="s">
         <v>180</v>
       </c>
-      <c r="J76" s="113" t="s">
+      <c r="J76" s="100" t="s">
         <v>131</v>
       </c>
       <c r="K76" s="56">
         <f>0.9</f>
         <v>0.9</v>
       </c>
-      <c r="L76" s="138">
+      <c r="L76" s="102">
         <f>K76+K77</f>
         <v>1.6600000000000001</v>
       </c>
       <c r="M76" s="61"/>
-      <c r="N76" s="113" t="s">
+      <c r="N76" s="100" t="s">
         <v>57</v>
       </c>
-      <c r="O76" s="113" t="s">
+      <c r="O76" s="100" t="s">
         <v>130</v>
       </c>
-      <c r="P76" s="95" t="s">
+      <c r="P76" s="92" t="s">
         <v>200</v>
       </c>
       <c r="Q76" s="38" t="s">
@@ -7965,7 +7965,7 @@
       <c r="R76" s="3">
         <v>0.78</v>
       </c>
-      <c r="S76" s="95">
+      <c r="S76" s="92">
         <f>R76+R77</f>
         <v>1.47</v>
       </c>
@@ -7973,57 +7973,57 @@
         <f>K76-R76</f>
         <v>0.12</v>
       </c>
-      <c r="U76" s="132">
+      <c r="U76" s="93">
         <f>L76-S76</f>
         <v>0.19000000000000017</v>
       </c>
-      <c r="V76" s="117">
+      <c r="V76" s="95">
         <f>U76/590</f>
         <v>3.2203389830508505E-4</v>
       </c>
-      <c r="W76" s="132">
+      <c r="W76" s="93">
         <f>(U76/L76)*100</f>
         <v>11.44578313253013</v>
       </c>
-      <c r="X76" s="100" t="s">
+      <c r="X76" s="98" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="77" spans="3:24" x14ac:dyDescent="0.35">
-      <c r="C77" s="101"/>
-      <c r="D77" s="97"/>
-      <c r="E77" s="101"/>
-      <c r="F77" s="101"/>
-      <c r="G77" s="101"/>
-      <c r="H77" s="101"/>
+      <c r="C77" s="99"/>
+      <c r="D77" s="104"/>
+      <c r="E77" s="99"/>
+      <c r="F77" s="99"/>
+      <c r="G77" s="99"/>
+      <c r="H77" s="99"/>
       <c r="I77" s="38" t="s">
         <v>182</v>
       </c>
-      <c r="J77" s="114"/>
+      <c r="J77" s="101"/>
       <c r="K77" s="56">
         <f>0.76</f>
         <v>0.76</v>
       </c>
-      <c r="L77" s="114"/>
+      <c r="L77" s="101"/>
       <c r="M77" s="61"/>
-      <c r="N77" s="114"/>
-      <c r="O77" s="114"/>
-      <c r="P77" s="95"/>
+      <c r="N77" s="101"/>
+      <c r="O77" s="101"/>
+      <c r="P77" s="92"/>
       <c r="Q77" s="38" t="s">
         <v>150</v>
       </c>
       <c r="R77" s="3">
         <v>0.69</v>
       </c>
-      <c r="S77" s="95"/>
+      <c r="S77" s="92"/>
       <c r="T77" s="57">
         <f t="shared" ref="T77" si="5">K77-R77</f>
         <v>7.0000000000000062E-2</v>
       </c>
-      <c r="U77" s="130"/>
-      <c r="V77" s="118"/>
-      <c r="W77" s="134"/>
-      <c r="X77" s="101"/>
+      <c r="U77" s="94"/>
+      <c r="V77" s="96"/>
+      <c r="W77" s="97"/>
+      <c r="X77" s="99"/>
     </row>
     <row r="87" spans="5:12" ht="29" x14ac:dyDescent="0.35">
       <c r="E87" s="25" t="s">
@@ -8398,43 +8398,436 @@
     </row>
   </sheetData>
   <mergeCells count="491">
-    <mergeCell ref="S76:S77"/>
-    <mergeCell ref="U76:U77"/>
-    <mergeCell ref="V76:V77"/>
-    <mergeCell ref="W76:W77"/>
-    <mergeCell ref="X76:X77"/>
-    <mergeCell ref="H76:H77"/>
-    <mergeCell ref="J76:J77"/>
-    <mergeCell ref="L76:L77"/>
-    <mergeCell ref="N76:N77"/>
-    <mergeCell ref="O76:O77"/>
-    <mergeCell ref="P76:P77"/>
-    <mergeCell ref="C76:C77"/>
-    <mergeCell ref="D76:D77"/>
-    <mergeCell ref="E76:E77"/>
-    <mergeCell ref="F76:F77"/>
-    <mergeCell ref="G76:G77"/>
-    <mergeCell ref="J74:J75"/>
-    <mergeCell ref="L74:L75"/>
-    <mergeCell ref="M74:M75"/>
-    <mergeCell ref="N74:N75"/>
-    <mergeCell ref="C74:C75"/>
-    <mergeCell ref="D74:D75"/>
-    <mergeCell ref="E74:E75"/>
-    <mergeCell ref="F74:F75"/>
-    <mergeCell ref="G74:G75"/>
-    <mergeCell ref="H74:H75"/>
-    <mergeCell ref="L72:L73"/>
-    <mergeCell ref="M72:M73"/>
-    <mergeCell ref="N72:N73"/>
-    <mergeCell ref="O72:O73"/>
-    <mergeCell ref="S74:S75"/>
-    <mergeCell ref="U74:U75"/>
-    <mergeCell ref="V74:V75"/>
-    <mergeCell ref="W74:W75"/>
-    <mergeCell ref="X74:X75"/>
-    <mergeCell ref="O74:O75"/>
-    <mergeCell ref="P74:P75"/>
+    <mergeCell ref="G4:L4"/>
+    <mergeCell ref="N4:S4"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="U6:U7"/>
+    <mergeCell ref="V6:V7"/>
+    <mergeCell ref="W6:W7"/>
+    <mergeCell ref="X6:X7"/>
+    <mergeCell ref="Y6:Y7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="L6:L7"/>
+    <mergeCell ref="M6:M7"/>
+    <mergeCell ref="N6:N7"/>
+    <mergeCell ref="O6:O7"/>
+    <mergeCell ref="P6:P7"/>
+    <mergeCell ref="S6:S7"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="H12:H13"/>
+    <mergeCell ref="O8:O9"/>
+    <mergeCell ref="P8:P9"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="M8:M9"/>
+    <mergeCell ref="N8:N9"/>
+    <mergeCell ref="Y12:Y13"/>
+    <mergeCell ref="J12:J13"/>
+    <mergeCell ref="L12:L13"/>
+    <mergeCell ref="M12:M13"/>
+    <mergeCell ref="N12:N13"/>
+    <mergeCell ref="O12:O13"/>
+    <mergeCell ref="P12:P13"/>
+    <mergeCell ref="X8:X9"/>
+    <mergeCell ref="Y8:Y9"/>
+    <mergeCell ref="V10:V11"/>
+    <mergeCell ref="S8:S9"/>
+    <mergeCell ref="U8:U9"/>
+    <mergeCell ref="V8:V9"/>
+    <mergeCell ref="W8:W9"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="S12:S13"/>
+    <mergeCell ref="U12:U13"/>
+    <mergeCell ref="V12:V13"/>
+    <mergeCell ref="W12:W13"/>
+    <mergeCell ref="X12:X13"/>
+    <mergeCell ref="Y14:Y15"/>
+    <mergeCell ref="B16:B18"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="E16:E18"/>
+    <mergeCell ref="F16:F18"/>
+    <mergeCell ref="G16:G18"/>
+    <mergeCell ref="H16:H18"/>
+    <mergeCell ref="J16:J18"/>
+    <mergeCell ref="L16:L18"/>
+    <mergeCell ref="M16:M18"/>
+    <mergeCell ref="P14:P15"/>
+    <mergeCell ref="S14:S15"/>
+    <mergeCell ref="U14:U15"/>
+    <mergeCell ref="V14:V15"/>
+    <mergeCell ref="W14:W15"/>
+    <mergeCell ref="X14:X15"/>
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="J14:J15"/>
+    <mergeCell ref="L14:L15"/>
+    <mergeCell ref="M14:M15"/>
+    <mergeCell ref="N14:N15"/>
+    <mergeCell ref="O14:O15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="X16:X18"/>
+    <mergeCell ref="Y16:Y18"/>
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="C19:C21"/>
+    <mergeCell ref="D19:D21"/>
+    <mergeCell ref="E19:E21"/>
+    <mergeCell ref="F19:F21"/>
+    <mergeCell ref="G19:G21"/>
+    <mergeCell ref="H19:H21"/>
+    <mergeCell ref="N16:N18"/>
+    <mergeCell ref="O16:O18"/>
+    <mergeCell ref="P16:P18"/>
+    <mergeCell ref="S16:S18"/>
+    <mergeCell ref="U16:U18"/>
+    <mergeCell ref="V16:V18"/>
+    <mergeCell ref="W19:W21"/>
+    <mergeCell ref="X19:X21"/>
+    <mergeCell ref="Y19:Y21"/>
+    <mergeCell ref="J19:J21"/>
+    <mergeCell ref="L19:L21"/>
+    <mergeCell ref="M19:M20"/>
+    <mergeCell ref="N19:N21"/>
+    <mergeCell ref="O19:O21"/>
+    <mergeCell ref="B22:B24"/>
+    <mergeCell ref="C22:C24"/>
+    <mergeCell ref="D22:D24"/>
+    <mergeCell ref="E22:E24"/>
+    <mergeCell ref="F22:F24"/>
+    <mergeCell ref="G22:G24"/>
+    <mergeCell ref="S19:S21"/>
+    <mergeCell ref="U19:U21"/>
+    <mergeCell ref="W16:W18"/>
+    <mergeCell ref="V19:V21"/>
+    <mergeCell ref="S22:S24"/>
+    <mergeCell ref="U22:U24"/>
+    <mergeCell ref="V22:V24"/>
+    <mergeCell ref="W22:W24"/>
+    <mergeCell ref="X22:X24"/>
+    <mergeCell ref="Y22:Y24"/>
+    <mergeCell ref="H22:H24"/>
+    <mergeCell ref="J22:J24"/>
+    <mergeCell ref="L22:L24"/>
+    <mergeCell ref="N22:N24"/>
+    <mergeCell ref="O22:O24"/>
+    <mergeCell ref="P22:P24"/>
+    <mergeCell ref="P19:P21"/>
+    <mergeCell ref="W25:W26"/>
+    <mergeCell ref="X25:X26"/>
+    <mergeCell ref="Y25:Y26"/>
+    <mergeCell ref="H25:H26"/>
+    <mergeCell ref="J25:J26"/>
+    <mergeCell ref="L25:L26"/>
+    <mergeCell ref="N25:N26"/>
+    <mergeCell ref="O25:O26"/>
+    <mergeCell ref="P25:P26"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="E27:E28"/>
+    <mergeCell ref="F27:F28"/>
+    <mergeCell ref="G27:G28"/>
+    <mergeCell ref="S25:S26"/>
+    <mergeCell ref="U25:U26"/>
+    <mergeCell ref="V25:V26"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="E25:E26"/>
+    <mergeCell ref="F25:F26"/>
+    <mergeCell ref="G25:G26"/>
+    <mergeCell ref="S27:S28"/>
+    <mergeCell ref="U27:U28"/>
+    <mergeCell ref="V27:V28"/>
+    <mergeCell ref="W27:W28"/>
+    <mergeCell ref="X27:X28"/>
+    <mergeCell ref="Y27:Y28"/>
+    <mergeCell ref="H27:H28"/>
+    <mergeCell ref="J27:J28"/>
+    <mergeCell ref="L27:L28"/>
+    <mergeCell ref="N27:N28"/>
+    <mergeCell ref="O27:O28"/>
+    <mergeCell ref="P27:P28"/>
+    <mergeCell ref="Y29:Y30"/>
+    <mergeCell ref="H29:H30"/>
+    <mergeCell ref="J29:J30"/>
+    <mergeCell ref="L29:L30"/>
+    <mergeCell ref="N29:N30"/>
+    <mergeCell ref="O29:O30"/>
+    <mergeCell ref="P29:P30"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="F29:F30"/>
+    <mergeCell ref="G29:G30"/>
+    <mergeCell ref="D31:D33"/>
+    <mergeCell ref="E31:E33"/>
+    <mergeCell ref="F31:F33"/>
+    <mergeCell ref="G31:G33"/>
+    <mergeCell ref="S29:S30"/>
+    <mergeCell ref="U29:U30"/>
+    <mergeCell ref="V29:V30"/>
+    <mergeCell ref="W29:W30"/>
+    <mergeCell ref="X29:X30"/>
+    <mergeCell ref="Y31:Y33"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="F34:F35"/>
+    <mergeCell ref="G34:G35"/>
+    <mergeCell ref="H34:H35"/>
+    <mergeCell ref="J34:J35"/>
+    <mergeCell ref="L34:L35"/>
+    <mergeCell ref="P31:P33"/>
+    <mergeCell ref="S31:S33"/>
+    <mergeCell ref="U31:U33"/>
+    <mergeCell ref="V31:V33"/>
+    <mergeCell ref="W31:W33"/>
+    <mergeCell ref="X31:X33"/>
+    <mergeCell ref="H31:H33"/>
+    <mergeCell ref="J31:J33"/>
+    <mergeCell ref="L31:L33"/>
+    <mergeCell ref="M31:M33"/>
+    <mergeCell ref="N31:N33"/>
+    <mergeCell ref="O31:O33"/>
+    <mergeCell ref="B31:B33"/>
+    <mergeCell ref="C31:C33"/>
+    <mergeCell ref="V34:V35"/>
+    <mergeCell ref="W34:W35"/>
+    <mergeCell ref="X34:X35"/>
+    <mergeCell ref="Y34:Y35"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="G36:G37"/>
+    <mergeCell ref="M34:M35"/>
+    <mergeCell ref="N34:N35"/>
+    <mergeCell ref="O34:O35"/>
+    <mergeCell ref="P34:P35"/>
+    <mergeCell ref="S34:S35"/>
+    <mergeCell ref="U34:U35"/>
+    <mergeCell ref="Y36:Y37"/>
+    <mergeCell ref="P36:P37"/>
+    <mergeCell ref="S36:S37"/>
+    <mergeCell ref="U36:U37"/>
+    <mergeCell ref="V36:V37"/>
+    <mergeCell ref="W36:W37"/>
+    <mergeCell ref="X36:X37"/>
+    <mergeCell ref="H36:H37"/>
+    <mergeCell ref="J36:J37"/>
+    <mergeCell ref="L36:L37"/>
+    <mergeCell ref="M36:M37"/>
+    <mergeCell ref="N36:N37"/>
+    <mergeCell ref="O36:O37"/>
+    <mergeCell ref="V38:V39"/>
+    <mergeCell ref="W38:W39"/>
+    <mergeCell ref="X38:X39"/>
+    <mergeCell ref="Y38:Y39"/>
+    <mergeCell ref="P38:P39"/>
+    <mergeCell ref="S38:S39"/>
+    <mergeCell ref="U38:U39"/>
+    <mergeCell ref="J38:J39"/>
+    <mergeCell ref="L38:L39"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="D40:D41"/>
+    <mergeCell ref="E40:E41"/>
+    <mergeCell ref="F40:F41"/>
+    <mergeCell ref="G40:G41"/>
+    <mergeCell ref="M38:M39"/>
+    <mergeCell ref="N38:N39"/>
+    <mergeCell ref="O38:O39"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="C38:C39"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="E38:E39"/>
+    <mergeCell ref="F38:F39"/>
+    <mergeCell ref="G38:G39"/>
+    <mergeCell ref="H38:H39"/>
+    <mergeCell ref="Y40:Y41"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="C42:C43"/>
+    <mergeCell ref="D42:D43"/>
+    <mergeCell ref="E42:E43"/>
+    <mergeCell ref="F42:F43"/>
+    <mergeCell ref="G42:G43"/>
+    <mergeCell ref="H42:H43"/>
+    <mergeCell ref="J42:J43"/>
+    <mergeCell ref="L42:L43"/>
+    <mergeCell ref="P40:P41"/>
+    <mergeCell ref="S40:S41"/>
+    <mergeCell ref="U40:U41"/>
+    <mergeCell ref="V40:V41"/>
+    <mergeCell ref="W40:W41"/>
+    <mergeCell ref="X40:X41"/>
+    <mergeCell ref="H40:H41"/>
+    <mergeCell ref="J40:J41"/>
+    <mergeCell ref="L40:L41"/>
+    <mergeCell ref="M40:M41"/>
+    <mergeCell ref="N40:N41"/>
+    <mergeCell ref="O40:O41"/>
+    <mergeCell ref="V42:V43"/>
+    <mergeCell ref="W42:W43"/>
+    <mergeCell ref="X42:X43"/>
+    <mergeCell ref="Y42:Y43"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="C44:C45"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="E44:E45"/>
+    <mergeCell ref="F44:F45"/>
+    <mergeCell ref="G44:G45"/>
+    <mergeCell ref="M42:M43"/>
+    <mergeCell ref="N42:N43"/>
+    <mergeCell ref="O42:O43"/>
+    <mergeCell ref="P42:P43"/>
+    <mergeCell ref="S42:S43"/>
+    <mergeCell ref="U42:U43"/>
+    <mergeCell ref="S44:S45"/>
+    <mergeCell ref="U44:U45"/>
+    <mergeCell ref="V44:V45"/>
+    <mergeCell ref="W44:W45"/>
+    <mergeCell ref="X44:X45"/>
+    <mergeCell ref="Y44:Y45"/>
+    <mergeCell ref="H44:H45"/>
+    <mergeCell ref="J44:J45"/>
+    <mergeCell ref="L44:L45"/>
+    <mergeCell ref="N44:N45"/>
+    <mergeCell ref="O44:O45"/>
+    <mergeCell ref="P44:P45"/>
+    <mergeCell ref="W46:W48"/>
+    <mergeCell ref="X46:X48"/>
+    <mergeCell ref="Y46:Y48"/>
+    <mergeCell ref="H46:H48"/>
+    <mergeCell ref="J46:J48"/>
+    <mergeCell ref="L46:L48"/>
+    <mergeCell ref="N46:N48"/>
+    <mergeCell ref="O46:O48"/>
+    <mergeCell ref="P46:P48"/>
+    <mergeCell ref="B49:B51"/>
+    <mergeCell ref="C49:C51"/>
+    <mergeCell ref="D49:D51"/>
+    <mergeCell ref="E49:E51"/>
+    <mergeCell ref="F49:F51"/>
+    <mergeCell ref="G49:G51"/>
+    <mergeCell ref="S46:S48"/>
+    <mergeCell ref="U46:U48"/>
+    <mergeCell ref="V46:V48"/>
+    <mergeCell ref="B46:B48"/>
+    <mergeCell ref="C46:C48"/>
+    <mergeCell ref="D46:D48"/>
+    <mergeCell ref="E46:E48"/>
+    <mergeCell ref="F46:F48"/>
+    <mergeCell ref="G46:G48"/>
+    <mergeCell ref="S49:S51"/>
+    <mergeCell ref="U49:U51"/>
+    <mergeCell ref="V49:V51"/>
+    <mergeCell ref="W49:W51"/>
+    <mergeCell ref="X49:X51"/>
+    <mergeCell ref="Y49:Y51"/>
+    <mergeCell ref="H49:H51"/>
+    <mergeCell ref="J49:J51"/>
+    <mergeCell ref="L49:L51"/>
+    <mergeCell ref="N49:N51"/>
+    <mergeCell ref="O49:O51"/>
+    <mergeCell ref="P49:P51"/>
+    <mergeCell ref="G60:L60"/>
+    <mergeCell ref="N60:S60"/>
+    <mergeCell ref="C62:C63"/>
+    <mergeCell ref="D62:D63"/>
+    <mergeCell ref="E62:E63"/>
+    <mergeCell ref="F62:F63"/>
+    <mergeCell ref="G62:G63"/>
+    <mergeCell ref="H62:H63"/>
+    <mergeCell ref="J62:J63"/>
+    <mergeCell ref="L62:L63"/>
+    <mergeCell ref="W62:W63"/>
+    <mergeCell ref="X62:X63"/>
+    <mergeCell ref="C64:C65"/>
+    <mergeCell ref="D64:D65"/>
+    <mergeCell ref="E64:E65"/>
+    <mergeCell ref="F64:F65"/>
+    <mergeCell ref="G64:G65"/>
+    <mergeCell ref="H64:H65"/>
+    <mergeCell ref="J64:J65"/>
+    <mergeCell ref="M62:M63"/>
+    <mergeCell ref="N62:N63"/>
+    <mergeCell ref="O62:O63"/>
+    <mergeCell ref="P62:P63"/>
+    <mergeCell ref="S62:S63"/>
+    <mergeCell ref="U62:U63"/>
+    <mergeCell ref="U64:U65"/>
+    <mergeCell ref="V64:V65"/>
+    <mergeCell ref="W64:W65"/>
+    <mergeCell ref="X64:X65"/>
+    <mergeCell ref="O64:O65"/>
+    <mergeCell ref="P64:P65"/>
+    <mergeCell ref="S64:S65"/>
+    <mergeCell ref="F66:F67"/>
+    <mergeCell ref="G66:G67"/>
+    <mergeCell ref="H66:H67"/>
+    <mergeCell ref="L64:L65"/>
+    <mergeCell ref="M64:M65"/>
+    <mergeCell ref="N64:N65"/>
+    <mergeCell ref="V62:V63"/>
+    <mergeCell ref="U66:U67"/>
+    <mergeCell ref="V66:V67"/>
+    <mergeCell ref="W66:W67"/>
+    <mergeCell ref="X66:X67"/>
+    <mergeCell ref="C68:C69"/>
+    <mergeCell ref="D68:D69"/>
+    <mergeCell ref="E68:E69"/>
+    <mergeCell ref="F68:F69"/>
+    <mergeCell ref="G68:G69"/>
+    <mergeCell ref="H68:H69"/>
+    <mergeCell ref="J66:J67"/>
+    <mergeCell ref="L66:L67"/>
+    <mergeCell ref="N66:N67"/>
+    <mergeCell ref="O66:O67"/>
+    <mergeCell ref="P66:P67"/>
+    <mergeCell ref="S66:S67"/>
+    <mergeCell ref="U68:U69"/>
+    <mergeCell ref="V68:V69"/>
+    <mergeCell ref="W68:W69"/>
+    <mergeCell ref="X68:X69"/>
+    <mergeCell ref="O68:O69"/>
+    <mergeCell ref="P68:P69"/>
+    <mergeCell ref="S68:S69"/>
+    <mergeCell ref="C66:C67"/>
+    <mergeCell ref="D66:D67"/>
+    <mergeCell ref="E66:E67"/>
+    <mergeCell ref="C70:C71"/>
+    <mergeCell ref="D70:D71"/>
+    <mergeCell ref="E70:E71"/>
+    <mergeCell ref="F70:F71"/>
+    <mergeCell ref="G70:G71"/>
+    <mergeCell ref="H70:H71"/>
+    <mergeCell ref="J68:J69"/>
+    <mergeCell ref="L68:L69"/>
+    <mergeCell ref="N68:N69"/>
     <mergeCell ref="S70:S71"/>
     <mergeCell ref="U70:U71"/>
     <mergeCell ref="V70:V71"/>
@@ -8459,436 +8852,43 @@
     <mergeCell ref="X72:X73"/>
     <mergeCell ref="H72:H73"/>
     <mergeCell ref="J72:J73"/>
-    <mergeCell ref="C70:C71"/>
-    <mergeCell ref="D70:D71"/>
-    <mergeCell ref="E70:E71"/>
-    <mergeCell ref="F70:F71"/>
-    <mergeCell ref="G70:G71"/>
-    <mergeCell ref="H70:H71"/>
-    <mergeCell ref="J68:J69"/>
-    <mergeCell ref="L68:L69"/>
-    <mergeCell ref="N68:N69"/>
-    <mergeCell ref="W66:W67"/>
-    <mergeCell ref="X66:X67"/>
-    <mergeCell ref="C68:C69"/>
-    <mergeCell ref="D68:D69"/>
-    <mergeCell ref="E68:E69"/>
-    <mergeCell ref="F68:F69"/>
-    <mergeCell ref="G68:G69"/>
-    <mergeCell ref="H68:H69"/>
-    <mergeCell ref="J66:J67"/>
-    <mergeCell ref="L66:L67"/>
-    <mergeCell ref="N66:N67"/>
-    <mergeCell ref="O66:O67"/>
-    <mergeCell ref="P66:P67"/>
-    <mergeCell ref="S66:S67"/>
-    <mergeCell ref="U68:U69"/>
-    <mergeCell ref="V68:V69"/>
-    <mergeCell ref="W68:W69"/>
-    <mergeCell ref="X68:X69"/>
-    <mergeCell ref="O68:O69"/>
-    <mergeCell ref="P68:P69"/>
-    <mergeCell ref="S68:S69"/>
-    <mergeCell ref="C66:C67"/>
-    <mergeCell ref="D66:D67"/>
-    <mergeCell ref="E66:E67"/>
-    <mergeCell ref="F66:F67"/>
-    <mergeCell ref="G66:G67"/>
-    <mergeCell ref="H66:H67"/>
-    <mergeCell ref="L64:L65"/>
-    <mergeCell ref="M64:M65"/>
-    <mergeCell ref="N64:N65"/>
-    <mergeCell ref="V62:V63"/>
-    <mergeCell ref="U66:U67"/>
-    <mergeCell ref="V66:V67"/>
-    <mergeCell ref="W62:W63"/>
-    <mergeCell ref="X62:X63"/>
-    <mergeCell ref="C64:C65"/>
-    <mergeCell ref="D64:D65"/>
-    <mergeCell ref="E64:E65"/>
-    <mergeCell ref="F64:F65"/>
-    <mergeCell ref="G64:G65"/>
-    <mergeCell ref="H64:H65"/>
-    <mergeCell ref="J64:J65"/>
-    <mergeCell ref="M62:M63"/>
-    <mergeCell ref="N62:N63"/>
-    <mergeCell ref="O62:O63"/>
-    <mergeCell ref="P62:P63"/>
-    <mergeCell ref="S62:S63"/>
-    <mergeCell ref="U62:U63"/>
-    <mergeCell ref="U64:U65"/>
-    <mergeCell ref="V64:V65"/>
-    <mergeCell ref="W64:W65"/>
-    <mergeCell ref="X64:X65"/>
-    <mergeCell ref="O64:O65"/>
-    <mergeCell ref="P64:P65"/>
-    <mergeCell ref="S64:S65"/>
-    <mergeCell ref="G60:L60"/>
-    <mergeCell ref="N60:S60"/>
-    <mergeCell ref="C62:C63"/>
-    <mergeCell ref="D62:D63"/>
-    <mergeCell ref="E62:E63"/>
-    <mergeCell ref="F62:F63"/>
-    <mergeCell ref="G62:G63"/>
-    <mergeCell ref="H62:H63"/>
-    <mergeCell ref="J62:J63"/>
-    <mergeCell ref="L62:L63"/>
-    <mergeCell ref="W49:W51"/>
-    <mergeCell ref="X49:X51"/>
-    <mergeCell ref="Y49:Y51"/>
-    <mergeCell ref="H49:H51"/>
-    <mergeCell ref="J49:J51"/>
-    <mergeCell ref="L49:L51"/>
-    <mergeCell ref="N49:N51"/>
-    <mergeCell ref="O49:O51"/>
-    <mergeCell ref="P49:P51"/>
-    <mergeCell ref="B49:B51"/>
-    <mergeCell ref="C49:C51"/>
-    <mergeCell ref="D49:D51"/>
-    <mergeCell ref="E49:E51"/>
-    <mergeCell ref="F49:F51"/>
-    <mergeCell ref="G49:G51"/>
-    <mergeCell ref="S46:S48"/>
-    <mergeCell ref="U46:U48"/>
-    <mergeCell ref="V46:V48"/>
-    <mergeCell ref="B46:B48"/>
-    <mergeCell ref="C46:C48"/>
-    <mergeCell ref="D46:D48"/>
-    <mergeCell ref="E46:E48"/>
-    <mergeCell ref="F46:F48"/>
-    <mergeCell ref="G46:G48"/>
-    <mergeCell ref="S49:S51"/>
-    <mergeCell ref="U49:U51"/>
-    <mergeCell ref="V49:V51"/>
-    <mergeCell ref="O44:O45"/>
-    <mergeCell ref="P44:P45"/>
-    <mergeCell ref="W46:W48"/>
-    <mergeCell ref="X46:X48"/>
-    <mergeCell ref="Y46:Y48"/>
-    <mergeCell ref="H46:H48"/>
-    <mergeCell ref="J46:J48"/>
-    <mergeCell ref="L46:L48"/>
-    <mergeCell ref="N46:N48"/>
-    <mergeCell ref="O46:O48"/>
-    <mergeCell ref="P46:P48"/>
-    <mergeCell ref="X42:X43"/>
-    <mergeCell ref="Y42:Y43"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="C44:C45"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="E44:E45"/>
-    <mergeCell ref="F44:F45"/>
-    <mergeCell ref="G44:G45"/>
-    <mergeCell ref="M42:M43"/>
-    <mergeCell ref="N42:N43"/>
-    <mergeCell ref="O42:O43"/>
-    <mergeCell ref="P42:P43"/>
-    <mergeCell ref="S42:S43"/>
-    <mergeCell ref="U42:U43"/>
-    <mergeCell ref="S44:S45"/>
-    <mergeCell ref="U44:U45"/>
-    <mergeCell ref="V44:V45"/>
-    <mergeCell ref="W44:W45"/>
-    <mergeCell ref="X44:X45"/>
-    <mergeCell ref="Y44:Y45"/>
-    <mergeCell ref="H44:H45"/>
-    <mergeCell ref="J44:J45"/>
-    <mergeCell ref="L44:L45"/>
-    <mergeCell ref="N44:N45"/>
-    <mergeCell ref="Y40:Y41"/>
-    <mergeCell ref="B42:B43"/>
-    <mergeCell ref="C42:C43"/>
-    <mergeCell ref="D42:D43"/>
-    <mergeCell ref="E42:E43"/>
-    <mergeCell ref="F42:F43"/>
-    <mergeCell ref="G42:G43"/>
-    <mergeCell ref="H42:H43"/>
-    <mergeCell ref="J42:J43"/>
-    <mergeCell ref="L42:L43"/>
-    <mergeCell ref="P40:P41"/>
-    <mergeCell ref="S40:S41"/>
-    <mergeCell ref="U40:U41"/>
-    <mergeCell ref="V40:V41"/>
-    <mergeCell ref="W40:W41"/>
-    <mergeCell ref="X40:X41"/>
-    <mergeCell ref="H40:H41"/>
-    <mergeCell ref="J40:J41"/>
-    <mergeCell ref="L40:L41"/>
-    <mergeCell ref="M40:M41"/>
-    <mergeCell ref="N40:N41"/>
-    <mergeCell ref="O40:O41"/>
-    <mergeCell ref="V42:V43"/>
-    <mergeCell ref="W42:W43"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="D40:D41"/>
-    <mergeCell ref="E40:E41"/>
-    <mergeCell ref="F40:F41"/>
-    <mergeCell ref="G40:G41"/>
-    <mergeCell ref="M38:M39"/>
-    <mergeCell ref="N38:N39"/>
-    <mergeCell ref="O38:O39"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="C38:C39"/>
-    <mergeCell ref="D38:D39"/>
-    <mergeCell ref="E38:E39"/>
-    <mergeCell ref="F38:F39"/>
-    <mergeCell ref="G38:G39"/>
-    <mergeCell ref="H38:H39"/>
-    <mergeCell ref="J36:J37"/>
-    <mergeCell ref="L36:L37"/>
-    <mergeCell ref="M36:M37"/>
-    <mergeCell ref="N36:N37"/>
-    <mergeCell ref="O36:O37"/>
-    <mergeCell ref="V38:V39"/>
-    <mergeCell ref="W38:W39"/>
-    <mergeCell ref="X38:X39"/>
-    <mergeCell ref="Y38:Y39"/>
-    <mergeCell ref="P38:P39"/>
-    <mergeCell ref="S38:S39"/>
-    <mergeCell ref="U38:U39"/>
-    <mergeCell ref="J38:J39"/>
-    <mergeCell ref="L38:L39"/>
-    <mergeCell ref="V34:V35"/>
-    <mergeCell ref="W34:W35"/>
-    <mergeCell ref="X34:X35"/>
-    <mergeCell ref="Y34:Y35"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="D36:D37"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="F36:F37"/>
-    <mergeCell ref="G36:G37"/>
-    <mergeCell ref="M34:M35"/>
-    <mergeCell ref="N34:N35"/>
-    <mergeCell ref="O34:O35"/>
-    <mergeCell ref="P34:P35"/>
-    <mergeCell ref="S34:S35"/>
-    <mergeCell ref="U34:U35"/>
-    <mergeCell ref="Y36:Y37"/>
-    <mergeCell ref="P36:P37"/>
-    <mergeCell ref="S36:S37"/>
-    <mergeCell ref="U36:U37"/>
-    <mergeCell ref="V36:V37"/>
-    <mergeCell ref="W36:W37"/>
-    <mergeCell ref="X36:X37"/>
-    <mergeCell ref="H36:H37"/>
-    <mergeCell ref="Y31:Y33"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="D34:D35"/>
-    <mergeCell ref="E34:E35"/>
-    <mergeCell ref="F34:F35"/>
-    <mergeCell ref="G34:G35"/>
-    <mergeCell ref="H34:H35"/>
-    <mergeCell ref="J34:J35"/>
-    <mergeCell ref="L34:L35"/>
-    <mergeCell ref="P31:P33"/>
-    <mergeCell ref="S31:S33"/>
-    <mergeCell ref="U31:U33"/>
-    <mergeCell ref="V31:V33"/>
-    <mergeCell ref="W31:W33"/>
-    <mergeCell ref="X31:X33"/>
-    <mergeCell ref="H31:H33"/>
-    <mergeCell ref="J31:J33"/>
-    <mergeCell ref="L31:L33"/>
-    <mergeCell ref="M31:M33"/>
-    <mergeCell ref="N31:N33"/>
-    <mergeCell ref="O31:O33"/>
-    <mergeCell ref="B31:B33"/>
-    <mergeCell ref="C31:C33"/>
-    <mergeCell ref="D31:D33"/>
-    <mergeCell ref="E31:E33"/>
-    <mergeCell ref="F31:F33"/>
-    <mergeCell ref="G31:G33"/>
-    <mergeCell ref="S29:S30"/>
-    <mergeCell ref="U29:U30"/>
-    <mergeCell ref="V29:V30"/>
-    <mergeCell ref="W29:W30"/>
-    <mergeCell ref="X29:X30"/>
-    <mergeCell ref="Y29:Y30"/>
-    <mergeCell ref="H29:H30"/>
-    <mergeCell ref="J29:J30"/>
-    <mergeCell ref="L29:L30"/>
-    <mergeCell ref="N29:N30"/>
-    <mergeCell ref="O29:O30"/>
-    <mergeCell ref="P29:P30"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="E29:E30"/>
-    <mergeCell ref="F29:F30"/>
-    <mergeCell ref="G29:G30"/>
-    <mergeCell ref="W27:W28"/>
-    <mergeCell ref="X27:X28"/>
-    <mergeCell ref="Y27:Y28"/>
-    <mergeCell ref="H27:H28"/>
-    <mergeCell ref="J27:J28"/>
-    <mergeCell ref="L27:L28"/>
-    <mergeCell ref="N27:N28"/>
-    <mergeCell ref="O27:O28"/>
-    <mergeCell ref="P27:P28"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="D27:D28"/>
-    <mergeCell ref="E27:E28"/>
-    <mergeCell ref="F27:F28"/>
-    <mergeCell ref="G27:G28"/>
-    <mergeCell ref="S25:S26"/>
-    <mergeCell ref="U25:U26"/>
-    <mergeCell ref="V25:V26"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="D25:D26"/>
-    <mergeCell ref="E25:E26"/>
-    <mergeCell ref="F25:F26"/>
-    <mergeCell ref="G25:G26"/>
-    <mergeCell ref="S27:S28"/>
-    <mergeCell ref="U27:U28"/>
-    <mergeCell ref="V27:V28"/>
-    <mergeCell ref="W25:W26"/>
-    <mergeCell ref="X25:X26"/>
-    <mergeCell ref="Y25:Y26"/>
-    <mergeCell ref="H25:H26"/>
-    <mergeCell ref="J25:J26"/>
-    <mergeCell ref="L25:L26"/>
-    <mergeCell ref="N25:N26"/>
-    <mergeCell ref="O25:O26"/>
-    <mergeCell ref="P25:P26"/>
-    <mergeCell ref="X22:X24"/>
-    <mergeCell ref="Y22:Y24"/>
-    <mergeCell ref="H22:H24"/>
-    <mergeCell ref="J22:J24"/>
-    <mergeCell ref="L22:L24"/>
-    <mergeCell ref="N22:N24"/>
-    <mergeCell ref="O22:O24"/>
-    <mergeCell ref="P22:P24"/>
-    <mergeCell ref="P19:P21"/>
-    <mergeCell ref="B22:B24"/>
-    <mergeCell ref="C22:C24"/>
-    <mergeCell ref="D22:D24"/>
-    <mergeCell ref="E22:E24"/>
-    <mergeCell ref="F22:F24"/>
-    <mergeCell ref="G22:G24"/>
-    <mergeCell ref="S19:S21"/>
-    <mergeCell ref="U19:U21"/>
-    <mergeCell ref="W16:W18"/>
-    <mergeCell ref="V19:V21"/>
-    <mergeCell ref="S22:S24"/>
-    <mergeCell ref="U22:U24"/>
-    <mergeCell ref="V22:V24"/>
-    <mergeCell ref="W22:W24"/>
-    <mergeCell ref="X16:X18"/>
-    <mergeCell ref="Y16:Y18"/>
-    <mergeCell ref="B19:B21"/>
-    <mergeCell ref="C19:C21"/>
-    <mergeCell ref="D19:D21"/>
-    <mergeCell ref="E19:E21"/>
-    <mergeCell ref="F19:F21"/>
-    <mergeCell ref="G19:G21"/>
-    <mergeCell ref="H19:H21"/>
-    <mergeCell ref="N16:N18"/>
-    <mergeCell ref="O16:O18"/>
-    <mergeCell ref="P16:P18"/>
-    <mergeCell ref="S16:S18"/>
-    <mergeCell ref="U16:U18"/>
-    <mergeCell ref="V16:V18"/>
-    <mergeCell ref="W19:W21"/>
-    <mergeCell ref="X19:X21"/>
-    <mergeCell ref="Y19:Y21"/>
-    <mergeCell ref="J19:J21"/>
-    <mergeCell ref="L19:L21"/>
-    <mergeCell ref="M19:M20"/>
-    <mergeCell ref="N19:N21"/>
-    <mergeCell ref="O19:O21"/>
-    <mergeCell ref="Y14:Y15"/>
-    <mergeCell ref="B16:B18"/>
-    <mergeCell ref="C16:C18"/>
-    <mergeCell ref="E16:E18"/>
-    <mergeCell ref="F16:F18"/>
-    <mergeCell ref="G16:G18"/>
-    <mergeCell ref="H16:H18"/>
-    <mergeCell ref="J16:J18"/>
-    <mergeCell ref="L16:L18"/>
-    <mergeCell ref="M16:M18"/>
-    <mergeCell ref="P14:P15"/>
-    <mergeCell ref="S14:S15"/>
-    <mergeCell ref="U14:U15"/>
-    <mergeCell ref="V14:V15"/>
-    <mergeCell ref="W14:W15"/>
-    <mergeCell ref="X14:X15"/>
-    <mergeCell ref="H14:H15"/>
-    <mergeCell ref="J14:J15"/>
-    <mergeCell ref="L14:L15"/>
-    <mergeCell ref="M14:M15"/>
-    <mergeCell ref="N14:N15"/>
-    <mergeCell ref="O14:O15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="S12:S13"/>
-    <mergeCell ref="U12:U13"/>
-    <mergeCell ref="V12:V13"/>
-    <mergeCell ref="W12:W13"/>
-    <mergeCell ref="X12:X13"/>
-    <mergeCell ref="Y12:Y13"/>
-    <mergeCell ref="J12:J13"/>
-    <mergeCell ref="L12:L13"/>
-    <mergeCell ref="M12:M13"/>
-    <mergeCell ref="N12:N13"/>
-    <mergeCell ref="O12:O13"/>
-    <mergeCell ref="P12:P13"/>
-    <mergeCell ref="X8:X9"/>
-    <mergeCell ref="Y8:Y9"/>
-    <mergeCell ref="V10:V11"/>
-    <mergeCell ref="S8:S9"/>
-    <mergeCell ref="U8:U9"/>
-    <mergeCell ref="V8:V9"/>
-    <mergeCell ref="W8:W9"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="H12:H13"/>
-    <mergeCell ref="O8:O9"/>
-    <mergeCell ref="P8:P9"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="L8:L9"/>
-    <mergeCell ref="M8:M9"/>
-    <mergeCell ref="N8:N9"/>
-    <mergeCell ref="U6:U7"/>
-    <mergeCell ref="V6:V7"/>
-    <mergeCell ref="W6:W7"/>
-    <mergeCell ref="X6:X7"/>
-    <mergeCell ref="Y6:Y7"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="L6:L7"/>
-    <mergeCell ref="M6:M7"/>
-    <mergeCell ref="N6:N7"/>
-    <mergeCell ref="O6:O7"/>
-    <mergeCell ref="P6:P7"/>
-    <mergeCell ref="S6:S7"/>
-    <mergeCell ref="G4:L4"/>
-    <mergeCell ref="N4:S4"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="L72:L73"/>
+    <mergeCell ref="M72:M73"/>
+    <mergeCell ref="N72:N73"/>
+    <mergeCell ref="O72:O73"/>
+    <mergeCell ref="S74:S75"/>
+    <mergeCell ref="U74:U75"/>
+    <mergeCell ref="V74:V75"/>
+    <mergeCell ref="W74:W75"/>
+    <mergeCell ref="X74:X75"/>
+    <mergeCell ref="O74:O75"/>
+    <mergeCell ref="P74:P75"/>
+    <mergeCell ref="C76:C77"/>
+    <mergeCell ref="D76:D77"/>
+    <mergeCell ref="E76:E77"/>
+    <mergeCell ref="F76:F77"/>
+    <mergeCell ref="G76:G77"/>
+    <mergeCell ref="J74:J75"/>
+    <mergeCell ref="L74:L75"/>
+    <mergeCell ref="M74:M75"/>
+    <mergeCell ref="N74:N75"/>
+    <mergeCell ref="C74:C75"/>
+    <mergeCell ref="D74:D75"/>
+    <mergeCell ref="E74:E75"/>
+    <mergeCell ref="F74:F75"/>
+    <mergeCell ref="G74:G75"/>
+    <mergeCell ref="H74:H75"/>
+    <mergeCell ref="S76:S77"/>
+    <mergeCell ref="U76:U77"/>
+    <mergeCell ref="V76:V77"/>
+    <mergeCell ref="W76:W77"/>
+    <mergeCell ref="X76:X77"/>
+    <mergeCell ref="H76:H77"/>
+    <mergeCell ref="J76:J77"/>
+    <mergeCell ref="L76:L77"/>
+    <mergeCell ref="N76:N77"/>
+    <mergeCell ref="O76:O77"/>
+    <mergeCell ref="P76:P77"/>
   </mergeCells>
   <conditionalFormatting sqref="G3:G4">
     <cfRule type="cellIs" dxfId="46" priority="41" operator="equal">
@@ -9072,11 +9072,11 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A3" s="148" t="s">
+      <c r="A3" s="149" t="s">
         <v>309</v>
       </c>
-      <c r="B3" s="148"/>
-      <c r="C3" s="148"/>
+      <c r="B3" s="149"/>
+      <c r="C3" s="149"/>
     </row>
     <row r="5" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="12" t="s">
@@ -10091,11 +10091,11 @@
       <c r="L1" s="74"/>
     </row>
     <row r="2" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="149" t="s">
+      <c r="A2" s="150" t="s">
         <v>219</v>
       </c>
-      <c r="B2" s="149"/>
-      <c r="C2" s="149"/>
+      <c r="B2" s="150"/>
+      <c r="C2" s="150"/>
       <c r="D2" s="74"/>
       <c r="E2" s="74"/>
       <c r="F2" s="74"/>
@@ -10303,7 +10303,7 @@
       <c r="J8" s="81"/>
       <c r="K8" s="81"/>
       <c r="L8" s="81"/>
-      <c r="M8" s="150"/>
+      <c r="M8" s="91"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9" s="81">
